--- a/Malaysia_Paddy_MLR_Analysis.xlsx
+++ b/Malaysia_Paddy_MLR_Analysis.xlsx
@@ -1,21 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\OneDrive\Desktop\emmanuel sir j\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546C1ED2-98BE-448A-BD7A-C42BE21F4F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Raw Data" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="MLR Results" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Analysis Data" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Dashboard" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Methodology Note" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Raw Data" sheetId="1" r:id="rId1"/>
+    <sheet name="MLR Results" sheetId="2" r:id="rId2"/>
+    <sheet name="Analysis Data" sheetId="3" r:id="rId3"/>
+    <sheet name="Dashboard" sheetId="4" r:id="rId4"/>
+    <sheet name="Methodology Note" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,541 +45,555 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="166">
   <si>
-    <t xml:space="preserve">Malaysia Paddy Statistics 1980–2019  |  Source: DOSM Table 9.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group 19 — Kwara State University  |  MLR: Average Yield ~ Planted Area + Rice Production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planted Area (Ha)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paddy Production (T)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rice Production (T)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average Yield (Kg/Ha)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predicted Yield (Kg/Ha)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residual (Kg/Ha)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018 P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019 e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVERAGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multiple Linear Regression — Full Statistical Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model Equation:  ŷ = 2981.1461  +  (-0.004403) × x₁  +  (0.002291) × x₂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A.  MODEL SUMMARY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R² (Coefficient of Determination)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model explains 99.92% of variance ✔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted R²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accounts for predictors; very strong ✔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root Mean Square Error (RMSE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average prediction error ≈ 14.72 Kg/Ha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-statistic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overall model significance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F p-value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p &lt; 0.001 → Model is significant ✔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No. of Observations (n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40 years of data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Degrees of Freedom — Regression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 predictors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Degrees of Freedom — Residual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n − k − 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B.  ANALYSIS OF VARIANCE (ANOVA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum of Squares (SS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">df</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean Square (MS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-stat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p-value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C.  REGRESSION COEFFICIENTS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">β (Coefficient)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Std Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t-value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI Lower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI Upper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intercept (β₀)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planted Area x₁ (β₁)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rice Production x₂ (β₂)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D.  ASSUMPTION CHECKS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test / Metric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verdict</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linearity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pearson r (x₁, ŷ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Near ±1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weak positive ✔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pearson r (x₂, ŷ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strong positive ✔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multicollinearity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIF — Planted Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt; 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High — note as limitation ⚠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIF — Rice Prod.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corr(x₁, x₂)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt; 0.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moderate (0.3588) ✔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homoscedasticity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visual residual plot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No funnel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acceptable ✔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Normality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shapiro-Wilk stat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shapiro-Wilk p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt; 0.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slight departure ⚠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analysis Data Tables — Used for Dashboard Charts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual Yield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predicted Yield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Std. Residual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planted Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rice Production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correlation Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rice Prod.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avg Yield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLR ANALYSIS DASHBOARD — Malaysia Paddy Statistics 1980–2019</t>
+    <t>Malaysia Paddy Statistics 1980–2019  |  Source: DOSM Table 9.1</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Planted Area (Ha)</t>
+  </si>
+  <si>
+    <t>Paddy Production (T)</t>
+  </si>
+  <si>
+    <t>Rice Production (T)</t>
+  </si>
+  <si>
+    <t>Average Yield (Kg/Ha)</t>
+  </si>
+  <si>
+    <t>Predicted Yield (Kg/Ha)</t>
+  </si>
+  <si>
+    <t>Residual (Kg/Ha)</t>
+  </si>
+  <si>
+    <t>1980</t>
+  </si>
+  <si>
+    <t>1981</t>
+  </si>
+  <si>
+    <t>1982</t>
+  </si>
+  <si>
+    <t>1983</t>
+  </si>
+  <si>
+    <t>1984</t>
+  </si>
+  <si>
+    <t>1985</t>
+  </si>
+  <si>
+    <t>1986</t>
+  </si>
+  <si>
+    <t>1987</t>
+  </si>
+  <si>
+    <t>1988</t>
+  </si>
+  <si>
+    <t>1989</t>
+  </si>
+  <si>
+    <t>1990</t>
+  </si>
+  <si>
+    <t>1991</t>
+  </si>
+  <si>
+    <t>1992</t>
+  </si>
+  <si>
+    <t>1993</t>
+  </si>
+  <si>
+    <t>1994</t>
+  </si>
+  <si>
+    <t>1995</t>
+  </si>
+  <si>
+    <t>1996</t>
+  </si>
+  <si>
+    <t>1997</t>
+  </si>
+  <si>
+    <t>1998</t>
+  </si>
+  <si>
+    <t>1999</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>2018 P</t>
+  </si>
+  <si>
+    <t>2019 e</t>
+  </si>
+  <si>
+    <t>AVERAGE</t>
+  </si>
+  <si>
+    <t>Multiple Linear Regression — Full Statistical Output</t>
+  </si>
+  <si>
+    <t>Model Equation:  ŷ = 2981.1461  +  (-0.004403) × x₁  +  (0.002291) × x₂</t>
+  </si>
+  <si>
+    <t>A.  MODEL SUMMARY</t>
+  </si>
+  <si>
+    <t>R² (Coefficient of Determination)</t>
+  </si>
+  <si>
+    <t>Model explains 99.92% of variance ✔</t>
+  </si>
+  <si>
+    <t>Adjusted R²</t>
+  </si>
+  <si>
+    <t>Accounts for predictors; very strong ✔</t>
+  </si>
+  <si>
+    <t>Root Mean Square Error (RMSE)</t>
+  </si>
+  <si>
+    <t>Average prediction error ≈ 14.72 Kg/Ha</t>
+  </si>
+  <si>
+    <t>F-statistic</t>
+  </si>
+  <si>
+    <t>Overall model significance</t>
+  </si>
+  <si>
+    <t>F p-value</t>
+  </si>
+  <si>
+    <t>p &lt; 0.001 → Model is significant ✔</t>
+  </si>
+  <si>
+    <t>No. of Observations (n)</t>
+  </si>
+  <si>
+    <t>40 years of data</t>
+  </si>
+  <si>
+    <t>Degrees of Freedom — Regression</t>
+  </si>
+  <si>
+    <t>2 predictors</t>
+  </si>
+  <si>
+    <t>Degrees of Freedom — Residual</t>
+  </si>
+  <si>
+    <t>n − k − 1</t>
+  </si>
+  <si>
+    <t>B.  ANALYSIS OF VARIANCE (ANOVA)</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Sum of Squares (SS)</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>Mean Square (MS)</t>
+  </si>
+  <si>
+    <t>F-stat</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>Residual</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>C.  REGRESSION COEFFICIENTS</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>β (Coefficient)</t>
+  </si>
+  <si>
+    <t>Std Error</t>
+  </si>
+  <si>
+    <t>t-value</t>
+  </si>
+  <si>
+    <t>95% CI Lower</t>
+  </si>
+  <si>
+    <t>95% CI Upper</t>
+  </si>
+  <si>
+    <t>Intercept (β₀)</t>
+  </si>
+  <si>
+    <t>Planted Area x₁ (β₁)</t>
+  </si>
+  <si>
+    <t>Rice Production x₂ (β₂)</t>
+  </si>
+  <si>
+    <t>D.  ASSUMPTION CHECKS</t>
+  </si>
+  <si>
+    <t>Assumption</t>
+  </si>
+  <si>
+    <t>Test / Metric</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Threshold</t>
+  </si>
+  <si>
+    <t>Verdict</t>
+  </si>
+  <si>
+    <t>Linearity</t>
+  </si>
+  <si>
+    <t>Pearson r (x₁, ŷ)</t>
+  </si>
+  <si>
+    <t>0.2316</t>
+  </si>
+  <si>
+    <t>Near ±1</t>
+  </si>
+  <si>
+    <t>Weak positive ✔</t>
+  </si>
+  <si>
+    <t>Pearson r (x₂, ŷ)</t>
+  </si>
+  <si>
+    <t>0.9907</t>
+  </si>
+  <si>
+    <t>Strong positive ✔</t>
+  </si>
+  <si>
+    <t>Multicollinearity</t>
+  </si>
+  <si>
+    <t>VIF — Planted Area</t>
+  </si>
+  <si>
+    <t>45.4851</t>
+  </si>
+  <si>
+    <t>&lt; 10</t>
+  </si>
+  <si>
+    <t>High — note as limitation ⚠</t>
+  </si>
+  <si>
+    <t>VIF — Rice Prod.</t>
+  </si>
+  <si>
+    <t>Corr(x₁, x₂)</t>
+  </si>
+  <si>
+    <t>0.3588</t>
+  </si>
+  <si>
+    <t>&lt; 0.80</t>
+  </si>
+  <si>
+    <t>Moderate (0.3588) ✔</t>
+  </si>
+  <si>
+    <t>Homoscedasticity</t>
+  </si>
+  <si>
+    <t>Visual residual plot</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>No funnel</t>
+  </si>
+  <si>
+    <t>Acceptable ✔</t>
+  </si>
+  <si>
+    <t>Normality</t>
+  </si>
+  <si>
+    <t>Shapiro-Wilk stat</t>
+  </si>
+  <si>
+    <t>0.7304</t>
+  </si>
+  <si>
+    <t>Shapiro-Wilk p</t>
+  </si>
+  <si>
+    <t>0.0000</t>
+  </si>
+  <si>
+    <t>&gt; 0.05</t>
+  </si>
+  <si>
+    <t>Slight departure ⚠</t>
+  </si>
+  <si>
+    <t>Analysis Data Tables — Used for Dashboard Charts</t>
+  </si>
+  <si>
+    <t>Actual Yield</t>
+  </si>
+  <si>
+    <t>Predicted Yield</t>
+  </si>
+  <si>
+    <t>Std. Residual</t>
+  </si>
+  <si>
+    <t>Planted Area</t>
+  </si>
+  <si>
+    <t>Rice Production</t>
+  </si>
+  <si>
+    <t>Correlation Matrix</t>
+  </si>
+  <si>
+    <t>Rice Prod.</t>
+  </si>
+  <si>
+    <t>Avg Yield</t>
   </si>
   <si>
     <t xml:space="preserve">  ŷ = 2981.1461  +  (-0.004403) × x₁  +  (0.002291) × x₂     |     R² = 0.9992     |     F = 22,018.22     |     p &lt; 0.001</t>
   </si>
   <si>
-    <t xml:space="preserve">R²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adj. R²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RMSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIF (x₁)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIF (x₂)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22,018.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24e-57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variance Explained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted Fit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avg Prediction Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model Significance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overall Significance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Methodology Note — Python (statsmodels) Replacing SPSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">█  Software Used:
+    <t>R²</t>
+  </si>
+  <si>
+    <t>Adj. R²</t>
+  </si>
+  <si>
+    <t>RMSE</t>
+  </si>
+  <si>
+    <t>VIF (x₁)</t>
+  </si>
+  <si>
+    <t>VIF (x₂)</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>0.9992</t>
+  </si>
+  <si>
+    <t>0.9991</t>
+  </si>
+  <si>
+    <t>14.72</t>
+  </si>
+  <si>
+    <t>22,018.22</t>
+  </si>
+  <si>
+    <t>1.24e-57</t>
+  </si>
+  <si>
+    <t>45.49</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Variance Explained</t>
+  </si>
+  <si>
+    <t>Adjusted Fit</t>
+  </si>
+  <si>
+    <t>Avg Prediction Error</t>
+  </si>
+  <si>
+    <t>Model Significance</t>
+  </si>
+  <si>
+    <t>Overall Significance</t>
+  </si>
+  <si>
+    <t>Observations</t>
+  </si>
+  <si>
+    <t>█  Software Used:
 Python 3 with the following libraries: pandas (data handling), numpy (numerical computation),
 scipy (statistical tests), statsmodels (OLS regression, ANOVA), openpyxl (this workbook).</t>
   </si>
   <si>
-    <t xml:space="preserve">█  Why Python Instead of SPSS:
+    <t>█  Why Python Instead of SPSS:
 Python's statsmodels OLS produces identical outputs to SPSS REGRESSION:
 coefficients, standard errors, t-statistics, p-values, R², ANOVA table, and residual diagnostics.</t>
   </si>
   <si>
-    <t xml:space="preserve">█  Step 1 — Data Collection:
+    <t>Methodology Note: Python (statsmodels) Replacing SPSS</t>
+  </si>
+  <si>
+    <t>█  Step 1: Data Collection:
 Data sourced from DOSM Table 9.1: Malaysia Paddy Statistics 1980–2019 (40 observations).
 Variables: Planted Area (Ha) = x₁, Rice Production (T) = x₂, Average Yield (Kg/Ha) = ŷ.</t>
   </si>
   <si>
-    <t xml:space="preserve">█  Step 2 — Linearity Check:
+    <t>█  Step 2: Linearity Check:
 Scatter plots of ŷ vs x₁ (r = 0.2316) and ŷ vs x₂ (r = 0.9907) confirm
 that linear relationships exist between the dependent and each independent variable.</t>
   </si>
   <si>
-    <t xml:space="preserve">█  Step 3 — Correlation Matrix + Multicollinearity:
+    <t>█  Step 3: Correlation Matrix + Multicollinearity:
 Correlation between x₁ and x₂: r = 0.3588 (moderate — acceptable).
 VIF(x₁) = 45.49, VIF(x₂) = 45.49. VIF &gt; 10 flags multicollinearity as a study limitation.</t>
   </si>
   <si>
-    <t xml:space="preserve">█  Step 4 — OLS Regression (statsmodels):
+    <t>█  Step 4: OLS Regression (statsmodels):
 β₀ = 2981.1461,  β₁ = -0.004403,  β₂ = 0.002291
 Final model: ŷ = 2981.1461 + (-0.004403)x₁ + (0.002291)x₂</t>
   </si>
   <si>
-    <t xml:space="preserve">█  Step 5 — ANOVA:
+    <t>█  Step 5: ANOVA:
 F(2, 37) = 22018.2158,  p = 1.2430e-57.
 Result: The MLR model is statistically significant at α = 0.001.</t>
   </si>
   <si>
-    <t xml:space="preserve">█  Step 6 — Model Fit:
+    <t>█  Step 6: Model Fit:
 R² = 0.999160 → the model explains 99.92% of the variation in average yield.
 Adjusted R² = 0.999115. RMSE = 14.7186 Kg/Ha.</t>
   </si>
   <si>
-    <t xml:space="preserve">█  Step 7 — Residual Diagnostics:
+    <t>█  Step 7: Residual Diagnostics:
 Shapiro-Wilk: W = 0.7304, p = 0.0000. Slight departure from normality noted as a limitation.
-Residual vs fitted plot shows no obvious funnel pattern — homoscedasticity is acceptable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">█  Interpretation:
+Residual vs fitted plot shows no obvious funnel pattern (homoscedasticity is acceptable.)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">█  Interpretation:
 A one-tonne increase in Rice Production is associated with a 0.002291 Kg/Ha increase in Average Yield.
 Planted Area has a small negative coefficient (−0.004403), indicating yield efficiency does not
-improve with area expansion alone — consistent with agronomic theory.</t>
+improve with area expansion alone, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">which is </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t>consistent with agronomic theory.</t>
+    </r>
+  </si>
+  <si>
+    <t>MLR ANALYSIS DASHBOARD</t>
+  </si>
+  <si>
+    <t>Group 19 MLR: Average Yield ~ Planted Area + Rice Production</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00;[RED]\-#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="0.000000"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="171" formatCode="0.00E+00"/>
-    <numFmt numFmtId="172" formatCode="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -569,215 +602,164 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="9"/>
       <color rgb="FF4A5568"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF1A7A6E"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF1A7A6E"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="9"/>
       <color rgb="FF888888"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFD45F3C"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFD45F3C"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF1A7A6E"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF276221"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF4A5568"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="13"/>
       <color rgb="FF1A7A6E"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="13"/>
       <color rgb="FFD45F3C"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="13"/>
       <color rgb="FFC9A227"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="13"/>
       <color rgb="FF4A5568"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="8"/>
       <color rgb="FF4A5568"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -844,16 +826,28 @@
         <bgColor rgb="FFF9F9F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor rgb="FF008080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFF7FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
@@ -868,7 +862,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
@@ -882,381 +876,281 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="89">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1315,15 +1209,33 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1332,7 +1244,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1340,7 +1252,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="en-GB" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1361,6 +1273,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -1369,7 +1282,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Analysis Data'!B3</c:f>
+              <c:f>'Analysis Data'!$B$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1379,12 +1292,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="1a7a6e"/>
-            </a:solidFill>
             <a:ln w="18000">
               <a:solidFill>
-                <a:srgbClr val="1a7a6e"/>
+                <a:srgbClr val="1A7A6E"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1393,15 +1303,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1409,8 +1327,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1418,9 +1337,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Analysis Data'!$A$4:$A$43</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>1980</c:v>
@@ -1542,8 +1462,8 @@
                 <c:pt idx="39">
                   <c:v>2019</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1675,13 +1595,18 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A65E-4A93-B030-7DEC6D9D4852}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Analysis Data'!C3</c:f>
+              <c:f>'Analysis Data'!$C$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1691,12 +1616,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="d45f3c"/>
-            </a:solidFill>
             <a:ln w="15120">
               <a:solidFill>
-                <a:srgbClr val="d45f3c"/>
+                <a:srgbClr val="D45F3C"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1705,15 +1627,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1721,8 +1651,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1730,9 +1661,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Analysis Data'!$A$4:$A$43</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>1980</c:v>
@@ -1854,8 +1786,8 @@
                 <c:pt idx="39">
                   <c:v>2019</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1987,7 +1919,20 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A65E-4A93-B030-7DEC6D9D4852}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -1995,7 +1940,7 @@
             </a:ln>
           </c:spPr>
         </c:hiLowLines>
-        <c:marker val="0"/>
+        <c:smooth val="0"/>
         <c:axId val="36411350"/>
         <c:axId val="84257750"/>
       </c:lineChart>
@@ -2013,7 +1958,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -2021,7 +1966,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-GB" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -2057,13 +2002,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="84257750"/>
@@ -2097,7 +2043,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -2105,7 +2051,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-GB" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -2141,13 +2087,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="36411350"/>
@@ -2175,37 +2122,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -2214,7 +2170,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -2222,7 +2178,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="en-GB" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -2243,6 +2199,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -2251,7 +2208,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Analysis Data'!F3</c:f>
+              <c:f>'Analysis Data'!$F$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2261,12 +2218,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="1a7a6e"/>
-            </a:solidFill>
             <a:ln w="18000">
               <a:solidFill>
-                <a:srgbClr val="1a7a6e"/>
+                <a:srgbClr val="1A7A6E"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2275,15 +2229,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2291,8 +2253,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -2300,9 +2263,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Analysis Data'!$A$4:$A$43</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>1980</c:v>
@@ -2424,8 +2388,8 @@
                 <c:pt idx="39">
                   <c:v>2019</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -2557,7 +2521,20 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B0C2-485C-A62F-3911A5134A14}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -2565,7 +2542,7 @@
             </a:ln>
           </c:spPr>
         </c:hiLowLines>
-        <c:marker val="0"/>
+        <c:smooth val="0"/>
         <c:axId val="2323802"/>
         <c:axId val="56506337"/>
       </c:lineChart>
@@ -2583,7 +2560,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -2591,7 +2568,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-GB" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -2627,13 +2604,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="56506337"/>
@@ -2667,7 +2645,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -2675,7 +2653,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-GB" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -2711,13 +2689,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="2323802"/>
@@ -2745,37 +2724,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -2784,7 +2772,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -2792,7 +2780,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="en-GB" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -2813,6 +2801,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -2821,7 +2810,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Analysis Data'!G3</c:f>
+              <c:f>'Analysis Data'!$G$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2831,12 +2820,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="c9a227"/>
-            </a:solidFill>
             <a:ln w="18000">
               <a:solidFill>
-                <a:srgbClr val="c9a227"/>
+                <a:srgbClr val="C9A227"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2845,15 +2831,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2861,8 +2855,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -2870,9 +2865,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Analysis Data'!$A$4:$A$43</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>1980</c:v>
@@ -2994,8 +2990,8 @@
                 <c:pt idx="39">
                   <c:v>2019</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -3127,7 +3123,20 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7F84-4B52-A9F9-2386CD646AA8}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -3135,7 +3144,7 @@
             </a:ln>
           </c:spPr>
         </c:hiLowLines>
-        <c:marker val="0"/>
+        <c:smooth val="0"/>
         <c:axId val="58796594"/>
         <c:axId val="11453849"/>
       </c:lineChart>
@@ -3153,7 +3162,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -3161,7 +3170,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-GB" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -3197,13 +3206,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="11453849"/>
@@ -3237,7 +3247,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -3245,7 +3255,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-GB" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -3281,13 +3291,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="58796594"/>
@@ -3315,37 +3326,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -3354,7 +3374,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -3362,7 +3382,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="en-GB" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -3383,6 +3403,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -3392,7 +3413,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Analysis Data'!D3</c:f>
+              <c:f>'Analysis Data'!$D$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3403,26 +3424,34 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="d45f3c"/>
+              <a:srgbClr val="D45F3C"/>
             </a:solidFill>
             <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="f9f9f9"/>
+                <a:srgbClr val="F9F9F9"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -3430,8 +3459,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -3439,9 +3469,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Analysis Data'!$A$4:$A$43</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>1980</c:v>
@@ -3563,14 +3594,14 @@
                 <c:pt idx="39">
                   <c:v>2019</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Analysis Data'!$D$4:$D$43</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00;[RED]\-#,##0.00</c:formatCode>
+                <c:formatCode>#,##0.00_);[Red]\(#,##0.00\)</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>7.41</c:v>
@@ -3579,7 +3610,7 @@
                   <c:v>5.93</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.81</c:v>
+                  <c:v>4.8099999999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>-3.09</c:v>
@@ -3609,7 +3640,7 @@
                   <c:v>2.4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-0.07</c:v>
+                  <c:v>-7.0000000000000007E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>-2.35</c:v>
@@ -3624,13 +3655,13 @@
                   <c:v>-7.79</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-4.27</c:v>
+                  <c:v>-4.2699999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>-7.75</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2.47</c:v>
+                  <c:v>-2.4700000000000002</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>-5.66</c:v>
@@ -3657,7 +3688,7 @@
                   <c:v>2.87</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>20.19</c:v>
+                  <c:v>20.190000000000001</c:v>
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>-0.86</c:v>
@@ -3681,7 +3712,7 @@
                   <c:v>-6.72</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-16.01</c:v>
+                  <c:v>-16.010000000000002</c:v>
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>-6.66</c:v>
@@ -3695,9 +3726,21 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BD7A-4868-998D-42BCFB625B0F}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
         <c:axId val="97315216"/>
         <c:axId val="49693433"/>
       </c:barChart>
@@ -3715,7 +3758,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -3723,7 +3766,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-GB" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -3759,13 +3802,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="49693433"/>
@@ -3799,7 +3843,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -3807,7 +3851,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-GB" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -3826,7 +3870,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="#,##0.00;[RED]\-#,##0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0.00_);[Red]\(#,##0.00\)" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3843,13 +3887,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="97315216"/>
@@ -3877,37 +3922,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -3916,7 +3970,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -3924,7 +3978,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -3945,6 +3999,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -3952,20 +4007,9 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"Yield vs Rice Prod."</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Yield vs Rice Prod.</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Yield vs Rice Prod.</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="1a7a6e"/>
-            </a:solidFill>
             <a:ln w="47520">
               <a:noFill/>
             </a:ln>
@@ -3975,20 +4019,28 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="1a7a6e"/>
+                <a:srgbClr val="1A7A6E"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -3996,8 +4048,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -4263,7 +4316,20 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8E41-4C92-8707-2796EE494258}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="83332137"/>
         <c:axId val="86402853"/>
       </c:scatterChart>
@@ -4291,7 +4357,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -4299,7 +4365,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -4335,13 +4401,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="86402853"/>
@@ -4372,7 +4439,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -4380,7 +4447,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -4416,13 +4483,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="83332137"/>
@@ -4450,37 +4518,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -4489,7 +4566,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -4497,7 +4574,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -4518,6 +4595,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -4525,20 +4603,9 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"Yield vs Planted Area"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Yield vs Planted Area</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Yield vs Planted Area</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="c9a227"/>
-            </a:solidFill>
             <a:ln w="47520">
               <a:noFill/>
             </a:ln>
@@ -4548,20 +4615,28 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="c9a227"/>
+                <a:srgbClr val="C9A227"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -4569,8 +4644,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -4836,7 +4912,20 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8E78-45E2-8404-8B76BBD21792}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="18228407"/>
         <c:axId val="89602800"/>
       </c:scatterChart>
@@ -4864,7 +4953,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -4872,7 +4961,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -4908,13 +4997,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="89602800"/>
@@ -4945,7 +5035,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -4953,7 +5043,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -4989,13 +5079,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="18228407"/>
@@ -5023,35 +5114,42 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -5065,14 +5163,20 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>170640</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="1762200"/>
-        <a:ext cx="5759640" cy="3599640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5095,14 +5199,20 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>170640</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 2"/>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5074920" y="1762200"/>
-        <a:ext cx="5759640" cy="3599640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5125,14 +5235,20 @@
       <xdr:row>45</xdr:row>
       <xdr:rowOff>170640</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 3"/>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="5572080"/>
-        <a:ext cx="5759640" cy="3599640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5155,14 +5271,20 @@
       <xdr:row>45</xdr:row>
       <xdr:rowOff>170640</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 4"/>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5074920" y="5572080"/>
-        <a:ext cx="5759640" cy="3599640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5185,14 +5307,20 @@
       <xdr:row>65</xdr:row>
       <xdr:rowOff>170640</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 5"/>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="9381960"/>
-        <a:ext cx="5759640" cy="3599640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5215,14 +5343,20 @@
       <xdr:row>65</xdr:row>
       <xdr:rowOff>170640</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 6"/>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5074920" y="9381960"/>
-        <a:ext cx="5759640" cy="3599640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5236,41 +5370,41 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -5278,12 +5412,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -5312,7 +5446,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -5333,7 +5467,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -5384,7 +5518,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -5402,1020 +5536,1019 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G45"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="87" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="3">
+        <v>716873</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2044604</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1318332</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2852</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2844.59</v>
+      </c>
+      <c r="G5" s="5">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>716873</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>2044604</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>1318332</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>2852</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>2844.59</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>7.41</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="B6" s="7">
+        <v>710789</v>
+      </c>
+      <c r="C6" s="7">
+        <v>2019900</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1302921</v>
+      </c>
+      <c r="E6" s="7">
+        <v>2842</v>
+      </c>
+      <c r="F6" s="8">
+        <v>2836.07</v>
+      </c>
+      <c r="G6" s="9">
+        <v>5.93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="9" t="n">
-        <v>710789</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>2019900</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>1302921</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>2842</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>2836.07</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>5.93</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="3">
+        <v>682070</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1883604</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1213281</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2762</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2757.19</v>
+      </c>
+      <c r="G7" s="5">
+        <v>4.8099999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>682070</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>1883604</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>1213281</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>2762</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>2757.19</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>4.81</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="B8" s="7">
+        <v>665813</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1734325</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1116937</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2605</v>
+      </c>
+      <c r="F8" s="8">
+        <v>2608.09</v>
+      </c>
+      <c r="G8" s="9">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="9" t="n">
-        <v>665813</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>1734325</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>1116937</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>2605</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>2608.09</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>-3.09</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="3">
+        <v>630833</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1571674</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1010279</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2491</v>
+      </c>
+      <c r="F9" s="4">
+        <v>2517.79</v>
+      </c>
+      <c r="G9" s="5">
+        <v>-26.79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>630833</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>1571674</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>1010279</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>2491</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>2517.79</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>-26.79</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="B10" s="7">
+        <v>656375</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1952914</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1257970</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2975</v>
+      </c>
+      <c r="F10" s="8">
+        <v>2972.69</v>
+      </c>
+      <c r="G10" s="9">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="9" t="n">
-        <v>656375</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>1952914</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>1257970</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>2975</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>2972.69</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="B11" s="3">
+        <v>650875</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1718215</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1104501</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2640</v>
+      </c>
+      <c r="F11" s="4">
+        <v>2645.37</v>
+      </c>
+      <c r="G11" s="5">
+        <v>-5.37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>650875</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>1718215</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>1104501</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>2640</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>2645.37</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>-5.37</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+      <c r="B12" s="7">
+        <v>658954</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1626699</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1046467</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2469</v>
+      </c>
+      <c r="F12" s="8">
+        <v>2476.87</v>
+      </c>
+      <c r="G12" s="9">
+        <v>-7.87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>658954</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>1626699</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>1046467</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>2469</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>2476.87</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>-7.87</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="B13" s="3">
+        <v>671755</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1696239</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1091478</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2525</v>
+      </c>
+      <c r="F13" s="4">
+        <v>2523.61</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>671755</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>1696239</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>1091478</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>2525</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>2523.61</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="B14" s="7">
+        <v>664137</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1743444</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1122617</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2625</v>
+      </c>
+      <c r="F14" s="8">
+        <v>2628.48</v>
+      </c>
+      <c r="G14" s="9">
+        <v>-3.48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>664137</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>1743444</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>1122617</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>2625</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>2628.48</v>
-      </c>
-      <c r="G14" s="11" t="n">
-        <v>-3.48</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="B15" s="3">
+        <v>680647</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1884984</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1215065</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2769</v>
+      </c>
+      <c r="F15" s="4">
+        <v>2767.54</v>
+      </c>
+      <c r="G15" s="5">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>680647</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>1884984</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1215065</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>2769</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>2767.54</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="B16" s="7">
+        <v>683640</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1926354</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1241796</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2818</v>
+      </c>
+      <c r="F16" s="8">
+        <v>2815.6</v>
+      </c>
+      <c r="G16" s="9">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="9" t="n">
-        <v>683640</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>1926354</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>1241796</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>2818</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>2815.6</v>
-      </c>
-      <c r="G16" s="11" t="n">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="B17" s="3">
+        <v>672753</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2012732</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1297914</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2992</v>
+      </c>
+      <c r="F17" s="4">
+        <v>2992.07</v>
+      </c>
+      <c r="G17" s="5">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>672753</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>2012732</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>1297914</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>2992</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>2992.07</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>-0.07</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+      <c r="B18" s="7">
+        <v>693434</v>
+      </c>
+      <c r="C18" s="7">
+        <v>2104447</v>
+      </c>
+      <c r="D18" s="7">
+        <v>1357432</v>
+      </c>
+      <c r="E18" s="7">
+        <v>3035</v>
+      </c>
+      <c r="F18" s="8">
+        <v>3037.35</v>
+      </c>
+      <c r="G18" s="9">
+        <v>-2.35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="9" t="n">
-        <v>693434</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>2104447</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>1357432</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>3035</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>3037.35</v>
-      </c>
-      <c r="G18" s="11" t="n">
-        <v>-2.35</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="B19" s="3">
+        <v>698624</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2138788</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1378945</v>
+      </c>
+      <c r="E19" s="3">
+        <v>3061</v>
+      </c>
+      <c r="F19" s="4">
+        <v>3063.78</v>
+      </c>
+      <c r="G19" s="5">
+        <v>-2.78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="5" t="n">
-        <v>698624</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>2138788</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>1378945</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>3061</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>3063.78</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>-2.78</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
+      <c r="B20" s="7">
+        <v>672787</v>
+      </c>
+      <c r="C20" s="7">
+        <v>2127271</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1372584</v>
+      </c>
+      <c r="E20" s="7">
+        <v>3162</v>
+      </c>
+      <c r="F20" s="8">
+        <v>3162.96</v>
+      </c>
+      <c r="G20" s="9">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="9" t="n">
-        <v>672787</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>2127271</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>1372584</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>3162</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>3162.96</v>
-      </c>
-      <c r="G20" s="11" t="n">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="B21" s="3">
+        <v>685468</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2228489</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1438794</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3251</v>
+      </c>
+      <c r="F21" s="4">
+        <v>3258.79</v>
+      </c>
+      <c r="G21" s="5">
+        <v>-7.79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="5" t="n">
-        <v>685468</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>2228489</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>1438794</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>3251</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>3258.79</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>-7.79</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
+      <c r="B22" s="7">
+        <v>690975</v>
+      </c>
+      <c r="C22" s="7">
+        <v>2119615</v>
+      </c>
+      <c r="D22" s="7">
+        <v>1367951</v>
+      </c>
+      <c r="E22" s="7">
+        <v>3068</v>
+      </c>
+      <c r="F22" s="8">
+        <v>3072.27</v>
+      </c>
+      <c r="G22" s="9">
+        <v>-4.2699999999999996</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="9" t="n">
-        <v>690975</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>2119615</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>1367951</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>3068</v>
-      </c>
-      <c r="F22" s="10" t="n">
-        <v>3072.27</v>
-      </c>
-      <c r="G22" s="11" t="n">
-        <v>-4.27</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="B23" s="3">
+        <v>674404</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1944240</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1256854</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2883</v>
+      </c>
+      <c r="F23" s="4">
+        <v>2890.75</v>
+      </c>
+      <c r="G23" s="5">
+        <v>-7.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="5" t="n">
-        <v>674404</v>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>1944240</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>1256854</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>2883</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>2890.75</v>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>-7.75</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
+      <c r="B24" s="7">
+        <v>692389</v>
+      </c>
+      <c r="C24" s="7">
+        <v>2036641</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1314437</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2941</v>
+      </c>
+      <c r="F24" s="8">
+        <v>2943.47</v>
+      </c>
+      <c r="G24" s="9">
+        <v>-2.4700000000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="9" t="n">
-        <v>692389</v>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>2036641</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>1314437</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>2941</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>2943.47</v>
-      </c>
-      <c r="G24" s="11" t="n">
-        <v>-2.47</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="B25" s="3">
+        <v>698702</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2140904</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1381662</v>
+      </c>
+      <c r="E25" s="3">
+        <v>3064</v>
+      </c>
+      <c r="F25" s="4">
+        <v>3069.66</v>
+      </c>
+      <c r="G25" s="5">
+        <v>-5.66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="5" t="n">
-        <v>698702</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>2140904</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>1381662</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>3064</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>3069.66</v>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>-5.66</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
+      <c r="B26" s="7">
+        <v>673634</v>
+      </c>
+      <c r="C26" s="7">
+        <v>2094995</v>
+      </c>
+      <c r="D26" s="7">
+        <v>1351461</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3110</v>
+      </c>
+      <c r="F26" s="8">
+        <v>3110.85</v>
+      </c>
+      <c r="G26" s="9">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="9" t="n">
-        <v>673634</v>
-      </c>
-      <c r="C26" s="9" t="n">
-        <v>2094995</v>
-      </c>
-      <c r="D26" s="9" t="n">
-        <v>1351461</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>3110</v>
-      </c>
-      <c r="F26" s="10" t="n">
-        <v>3110.85</v>
-      </c>
-      <c r="G26" s="11" t="n">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="B27" s="3">
+        <v>678544</v>
+      </c>
+      <c r="C27" s="3">
+        <v>2197351</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1415117</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3238</v>
+      </c>
+      <c r="F27" s="4">
+        <v>3235.04</v>
+      </c>
+      <c r="G27" s="5">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>678544</v>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>2197351</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>1415117</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>3238</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>3235.04</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>2.96</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
+      <c r="B28" s="7">
+        <v>671820</v>
+      </c>
+      <c r="C28" s="7">
+        <v>2257037</v>
+      </c>
+      <c r="D28" s="7">
+        <v>1453137</v>
+      </c>
+      <c r="E28" s="7">
+        <v>3360</v>
+      </c>
+      <c r="F28" s="8">
+        <v>3351.73</v>
+      </c>
+      <c r="G28" s="9">
+        <v>8.27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="9" t="n">
-        <v>671820</v>
-      </c>
-      <c r="C28" s="9" t="n">
-        <v>2257037</v>
-      </c>
-      <c r="D28" s="9" t="n">
-        <v>1453137</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>3360</v>
-      </c>
-      <c r="F28" s="10" t="n">
-        <v>3351.73</v>
-      </c>
-      <c r="G28" s="11" t="n">
-        <v>8.27</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+      <c r="B29" s="3">
+        <v>676310</v>
+      </c>
+      <c r="C29" s="3">
+        <v>2291353</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1467052</v>
+      </c>
+      <c r="E29" s="3">
+        <v>3434</v>
+      </c>
+      <c r="F29" s="4">
+        <v>3363.84</v>
+      </c>
+      <c r="G29" s="5">
+        <v>70.16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="5" t="n">
-        <v>676310</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>2291353</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>1467052</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>3434</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>3363.84</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>70.16</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
+      <c r="B30" s="7">
+        <v>666781</v>
+      </c>
+      <c r="C30" s="7">
+        <v>2314378</v>
+      </c>
+      <c r="D30" s="7">
+        <v>1490015</v>
+      </c>
+      <c r="E30" s="7">
+        <v>3471</v>
+      </c>
+      <c r="F30" s="8">
+        <v>3458.39</v>
+      </c>
+      <c r="G30" s="9">
+        <v>12.61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="9" t="n">
-        <v>666781</v>
-      </c>
-      <c r="C30" s="9" t="n">
-        <v>2314378</v>
-      </c>
-      <c r="D30" s="9" t="n">
-        <v>1490015</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>3471</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>3458.39</v>
-      </c>
-      <c r="G30" s="11" t="n">
-        <v>12.61</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+      <c r="B31" s="3">
+        <v>676034</v>
+      </c>
+      <c r="C31" s="3">
+        <v>2187519</v>
+      </c>
+      <c r="D31" s="3">
+        <v>1407220</v>
+      </c>
+      <c r="E31" s="3">
+        <v>3236</v>
+      </c>
+      <c r="F31" s="4">
+        <v>3228</v>
+      </c>
+      <c r="G31" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="5" t="n">
-        <v>676034</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>2187519</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>1407220</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>3236</v>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>3228</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
+      <c r="B32" s="7">
+        <v>676111</v>
+      </c>
+      <c r="C32" s="7">
+        <v>2375604</v>
+      </c>
+      <c r="D32" s="7">
+        <v>1530971</v>
+      </c>
+      <c r="E32" s="7">
+        <v>3514</v>
+      </c>
+      <c r="F32" s="8">
+        <v>3511.13</v>
+      </c>
+      <c r="G32" s="9">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="9" t="n">
-        <v>676111</v>
-      </c>
-      <c r="C32" s="9" t="n">
-        <v>2375604</v>
-      </c>
-      <c r="D32" s="9" t="n">
-        <v>1530971</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>3514</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>3511.13</v>
-      </c>
-      <c r="G32" s="11" t="n">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+      <c r="B33" s="3">
+        <v>656602</v>
+      </c>
+      <c r="C33" s="3">
+        <v>2353032</v>
+      </c>
+      <c r="D33" s="3">
+        <v>1516470</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3584</v>
+      </c>
+      <c r="F33" s="4">
+        <v>3563.81</v>
+      </c>
+      <c r="G33" s="5">
+        <v>20.190000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="5" t="n">
-        <v>656602</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>2353032</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>1516470</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>3584</v>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>3563.81</v>
-      </c>
-      <c r="G33" s="7" t="n">
-        <v>20.19</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="s">
+      <c r="B34" s="7">
+        <v>674928</v>
+      </c>
+      <c r="C34" s="7">
+        <v>2511043</v>
+      </c>
+      <c r="D34" s="7">
+        <v>1620259</v>
+      </c>
+      <c r="E34" s="7">
+        <v>3720</v>
+      </c>
+      <c r="F34" s="8">
+        <v>3720.86</v>
+      </c>
+      <c r="G34" s="9">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="9" t="n">
-        <v>674928</v>
-      </c>
-      <c r="C34" s="9" t="n">
-        <v>2511043</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>1620259</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>3720</v>
-      </c>
-      <c r="F34" s="10" t="n">
-        <v>3720.86</v>
-      </c>
-      <c r="G34" s="11" t="n">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
+      <c r="B35" s="3">
+        <v>677884</v>
+      </c>
+      <c r="C35" s="3">
+        <v>2464831</v>
+      </c>
+      <c r="D35" s="3">
+        <v>1588457</v>
+      </c>
+      <c r="E35" s="3">
+        <v>3636</v>
+      </c>
+      <c r="F35" s="4">
+        <v>3635</v>
+      </c>
+      <c r="G35" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="5" t="n">
-        <v>677884</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>2464831</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>1588457</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>3636</v>
-      </c>
-      <c r="F35" s="6" t="n">
-        <v>3635</v>
-      </c>
-      <c r="G35" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="s">
+      <c r="B36" s="7">
+        <v>687940</v>
+      </c>
+      <c r="C36" s="7">
+        <v>2578519</v>
+      </c>
+      <c r="D36" s="7">
+        <v>1661260</v>
+      </c>
+      <c r="E36" s="7">
+        <v>3748</v>
+      </c>
+      <c r="F36" s="8">
+        <v>3757.48</v>
+      </c>
+      <c r="G36" s="9">
+        <v>-9.48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="9" t="n">
-        <v>687940</v>
-      </c>
-      <c r="C36" s="9" t="n">
-        <v>2578519</v>
-      </c>
-      <c r="D36" s="9" t="n">
-        <v>1661260</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>3748</v>
-      </c>
-      <c r="F36" s="10" t="n">
-        <v>3757.48</v>
-      </c>
-      <c r="G36" s="11" t="n">
-        <v>-9.48</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+      <c r="B37" s="3">
+        <v>684545</v>
+      </c>
+      <c r="C37" s="3">
+        <v>2599382</v>
+      </c>
+      <c r="D37" s="3">
+        <v>1674981</v>
+      </c>
+      <c r="E37" s="3">
+        <v>3797</v>
+      </c>
+      <c r="F37" s="4">
+        <v>3803.86</v>
+      </c>
+      <c r="G37" s="5">
+        <v>-6.86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="5" t="n">
-        <v>684545</v>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>2599382</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>1674981</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>3797</v>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>3803.86</v>
-      </c>
-      <c r="G37" s="7" t="n">
-        <v>-6.86</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="s">
+      <c r="B38" s="7">
+        <v>671679</v>
+      </c>
+      <c r="C38" s="7">
+        <v>2603654</v>
+      </c>
+      <c r="D38" s="7">
+        <v>1677368</v>
+      </c>
+      <c r="E38" s="7">
+        <v>3876</v>
+      </c>
+      <c r="F38" s="8">
+        <v>3865.98</v>
+      </c>
+      <c r="G38" s="9">
+        <v>10.02</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="9" t="n">
-        <v>671679</v>
-      </c>
-      <c r="C38" s="9" t="n">
-        <v>2603654</v>
-      </c>
-      <c r="D38" s="9" t="n">
-        <v>1677368</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>3876</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>3865.98</v>
-      </c>
-      <c r="G38" s="11" t="n">
-        <v>10.02</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+      <c r="B39" s="3">
+        <v>679239</v>
+      </c>
+      <c r="C39" s="3">
+        <v>2848560</v>
+      </c>
+      <c r="D39" s="3">
+        <v>1834831</v>
+      </c>
+      <c r="E39" s="3">
+        <v>4194</v>
+      </c>
+      <c r="F39" s="4">
+        <v>4193.37</v>
+      </c>
+      <c r="G39" s="5">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="5" t="n">
-        <v>679239</v>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>2848560</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>1834831</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>4194</v>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>4193.37</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
+      <c r="B40" s="7">
+        <v>681559</v>
+      </c>
+      <c r="C40" s="7">
+        <v>2741404</v>
+      </c>
+      <c r="D40" s="7">
+        <v>1767407</v>
+      </c>
+      <c r="E40" s="7">
+        <v>4022</v>
+      </c>
+      <c r="F40" s="8">
+        <v>4028.72</v>
+      </c>
+      <c r="G40" s="9">
+        <v>-6.72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="9" t="n">
-        <v>681559</v>
-      </c>
-      <c r="C40" s="9" t="n">
-        <v>2741404</v>
-      </c>
-      <c r="D40" s="9" t="n">
-        <v>1767407</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>4022</v>
-      </c>
-      <c r="F40" s="10" t="n">
-        <v>4028.72</v>
-      </c>
-      <c r="G40" s="11" t="n">
-        <v>-6.72</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
+      <c r="B41" s="3">
+        <v>688770</v>
+      </c>
+      <c r="C41" s="3">
+        <v>2739606</v>
+      </c>
+      <c r="D41" s="3">
+        <v>1766115</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3978</v>
+      </c>
+      <c r="F41" s="4">
+        <v>3994.01</v>
+      </c>
+      <c r="G41" s="5">
+        <v>-16.010000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="5" t="n">
-        <v>688770</v>
-      </c>
-      <c r="C41" s="5" t="n">
-        <v>2739606</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>1766115</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>3978</v>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>3994.01</v>
-      </c>
-      <c r="G41" s="7" t="n">
-        <v>-16.01</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8" t="s">
+      <c r="B42" s="7">
+        <v>685548</v>
+      </c>
+      <c r="C42" s="7">
+        <v>2570513</v>
+      </c>
+      <c r="D42" s="7">
+        <v>1656302</v>
+      </c>
+      <c r="E42" s="7">
+        <v>3750</v>
+      </c>
+      <c r="F42" s="8">
+        <v>3756.66</v>
+      </c>
+      <c r="G42" s="9">
+        <v>-6.66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="9" t="n">
-        <v>685548</v>
-      </c>
-      <c r="C42" s="9" t="n">
-        <v>2570513</v>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>1656302</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>3750</v>
-      </c>
-      <c r="F42" s="10" t="n">
-        <v>3756.66</v>
-      </c>
-      <c r="G42" s="11" t="n">
-        <v>-6.66</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
+      <c r="B43" s="3">
+        <v>700306</v>
+      </c>
+      <c r="C43" s="3">
+        <v>2639916</v>
+      </c>
+      <c r="D43" s="3">
+        <v>1700231</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3770</v>
+      </c>
+      <c r="F43" s="4">
+        <v>3792.3</v>
+      </c>
+      <c r="G43" s="5">
+        <v>-22.3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B43" s="5" t="n">
-        <v>700306</v>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>2639916</v>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>1700231</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>3770</v>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>3792.3</v>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>-22.3</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
+      <c r="B44" s="7">
+        <v>684416</v>
+      </c>
+      <c r="C44" s="7">
+        <v>2912203</v>
+      </c>
+      <c r="D44" s="7">
+        <v>1876922</v>
+      </c>
+      <c r="E44" s="7">
+        <v>4255</v>
+      </c>
+      <c r="F44" s="8">
+        <v>4266.99</v>
+      </c>
+      <c r="G44" s="9">
+        <v>-11.99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B44" s="9" t="n">
-        <v>684416</v>
-      </c>
-      <c r="C44" s="9" t="n">
-        <v>2912203</v>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>1876922</v>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>4255</v>
-      </c>
-      <c r="F44" s="10" t="n">
-        <v>4266.99</v>
-      </c>
-      <c r="G44" s="11" t="n">
-        <v>-11.99</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B45" s="13" t="n">
-        <f aca="false">AVERAGE(B5:B44)</f>
-        <v>678623.675</v>
-      </c>
-      <c r="C45" s="13" t="n">
-        <f aca="false">AVERAGE(C5:C44)</f>
-        <v>2198424.575</v>
-      </c>
-      <c r="D45" s="13" t="n">
-        <f aca="false">AVERAGE(D5:D44)</f>
+      <c r="B45" s="11">
+        <f t="shared" ref="B45:G45" si="0">AVERAGE(B5:B44)</f>
+        <v>678623.67500000005</v>
+      </c>
+      <c r="C45" s="11">
+        <f t="shared" si="0"/>
+        <v>2198424.5750000002</v>
+      </c>
+      <c r="D45" s="11">
+        <f t="shared" si="0"/>
         <v>1416594.825</v>
       </c>
-      <c r="E45" s="13" t="n">
-        <f aca="false">AVERAGE(E5:E44)</f>
-        <v>3238.075</v>
-      </c>
-      <c r="F45" s="13" t="n">
-        <f aca="false">AVERAGE(F5:F44)</f>
-        <v>3238.07525</v>
-      </c>
-      <c r="G45" s="13" t="n">
-        <f aca="false">AVERAGE(G5:G44)</f>
-        <v>-0.000250000000000157</v>
+      <c r="E45" s="11">
+        <f t="shared" si="0"/>
+        <v>3238.0749999999998</v>
+      </c>
+      <c r="F45" s="11">
+        <f t="shared" si="0"/>
+        <v>3238.0752499999994</v>
+      </c>
+      <c r="G45" s="11">
+        <f t="shared" si="0"/>
+        <v>-2.4999999999999469E-4</v>
       </c>
     </row>
   </sheetData>
@@ -6423,502 +6556,494 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H38"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="16"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="71" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+    </row>
+    <row r="2" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-    </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+    </row>
+    <row r="4" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-    </row>
-    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+      <c r="B5" s="13">
+        <v>0.99916049196273504</v>
+      </c>
+      <c r="C5" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="18" t="n">
-        <v>0.999160491962735</v>
-      </c>
-      <c r="C5" s="19" t="s">
+      <c r="D5" s="70"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="19"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
+      <c r="B6" s="15">
+        <v>0.99911511314990997</v>
+      </c>
+      <c r="C6" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="21" t="n">
-        <v>0.99911511314991</v>
-      </c>
-      <c r="C6" s="22" t="s">
+      <c r="D6" s="66"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="22"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+      <c r="B7" s="16">
+        <v>14.7186420784218</v>
+      </c>
+      <c r="C7" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="23" t="n">
-        <v>14.7186420784218</v>
-      </c>
-      <c r="C7" s="19" t="s">
+      <c r="D7" s="70"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="19"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
+      <c r="B8" s="17">
+        <v>22018.2157654248</v>
+      </c>
+      <c r="C8" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="D8" s="66"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="18">
+        <v>1.2429678031647E-57</v>
+      </c>
+      <c r="C9" s="70" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="70"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="19">
+        <v>40</v>
+      </c>
+      <c r="C10" s="66" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="66"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="20">
+        <v>2</v>
+      </c>
+      <c r="C11" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="70"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="19">
+        <v>37</v>
+      </c>
+      <c r="C12" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="66"/>
+    </row>
+    <row r="15" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="67" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="67"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="23">
+        <v>9539983.1532885693</v>
+      </c>
+      <c r="C17" s="24">
+        <v>2</v>
+      </c>
+      <c r="D17" s="23">
+        <v>4769991.5766442902</v>
+      </c>
+      <c r="E17" s="25">
         <v>22018.2157654248</v>
       </c>
-      <c r="C8" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="22"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="25" t="n">
-        <v>1.2429678031647E-057</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="26" t="n">
-        <v>40</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="22"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="19"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="26" t="n">
+      <c r="F17" s="26">
+        <v>1.2429678031647E-57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="28">
+        <v>8015.6217114095198</v>
+      </c>
+      <c r="C18" s="29">
         <v>37</v>
       </c>
-      <c r="C12" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="22"/>
-    </row>
-    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="29" t="s">
+      <c r="D18" s="28">
+        <v>216.63842463269</v>
+      </c>
+      <c r="E18" s="30"/>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="32">
+        <v>9547998.7750000004</v>
+      </c>
+      <c r="C19" s="33">
+        <v>39</v>
+      </c>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="34"/>
+    </row>
+    <row r="22" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="29" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="31" t="n">
-        <v>9539983.15328857</v>
-      </c>
-      <c r="C17" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="31" t="n">
-        <v>4769991.57664429</v>
-      </c>
-      <c r="E17" s="33" t="n">
-        <v>22018.2157654248</v>
-      </c>
-      <c r="F17" s="34" t="n">
-        <v>1.2429678031647E-057</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="36" t="n">
-        <v>8015.62171140952</v>
-      </c>
-      <c r="C18" s="37" t="n">
-        <v>37</v>
-      </c>
-      <c r="D18" s="36" t="n">
-        <v>216.63842463269</v>
-      </c>
-      <c r="E18" s="38"/>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="B19" s="40" t="n">
-        <v>9547998.775</v>
-      </c>
-      <c r="C19" s="41" t="n">
-        <v>39</v>
-      </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="42"/>
-    </row>
-    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="B22" s="44"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" s="12" t="s">
+      <c r="F23" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="E23" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="12" t="s">
+      <c r="G23" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G23" s="12" t="s">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="36" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="45" t="s">
+      <c r="B24" s="37">
+        <v>2981.1460559164502</v>
+      </c>
+      <c r="C24" s="38">
+        <v>102.647405694776</v>
+      </c>
+      <c r="D24" s="39">
+        <v>29.042585496811601</v>
+      </c>
+      <c r="E24" s="40">
+        <v>4.5523609146367302E-27</v>
+      </c>
+      <c r="F24" s="38">
+        <v>2773.1626561481999</v>
+      </c>
+      <c r="G24" s="38">
+        <v>3189.1294556847001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="B24" s="46" t="n">
-        <v>2981.14605591645</v>
-      </c>
-      <c r="C24" s="47" t="n">
-        <v>102.647405694776</v>
-      </c>
-      <c r="D24" s="48" t="n">
-        <v>29.0425854968116</v>
-      </c>
-      <c r="E24" s="49" t="n">
-        <v>4.55236091463673E-027</v>
-      </c>
-      <c r="F24" s="47" t="n">
-        <v>2773.1626561482</v>
-      </c>
-      <c r="G24" s="47" t="n">
-        <v>3189.1294556847</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="50" t="s">
+      <c r="B25" s="42">
+        <v>-4.4028942452379698E-3</v>
+      </c>
+      <c r="C25" s="43">
+        <v>1.5803544675348401E-4</v>
+      </c>
+      <c r="D25" s="44">
+        <v>-27.860168941123401</v>
+      </c>
+      <c r="E25" s="45">
+        <v>1.9846180181760099E-26</v>
+      </c>
+      <c r="F25" s="43">
+        <v>-4.7231044763413202E-3</v>
+      </c>
+      <c r="G25" s="43">
+        <v>-4.0826840141346297E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="B25" s="51" t="n">
-        <v>-0.00440289424523797</v>
-      </c>
-      <c r="C25" s="52" t="n">
-        <v>0.000158035446753484</v>
-      </c>
-      <c r="D25" s="53" t="n">
-        <v>-27.8601689411234</v>
-      </c>
-      <c r="E25" s="54" t="n">
-        <v>1.98461801817601E-026</v>
-      </c>
-      <c r="F25" s="52" t="n">
-        <v>-0.00472310447634132</v>
-      </c>
-      <c r="G25" s="52" t="n">
-        <v>-0.00408268401413463</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="45" t="s">
+      <c r="B26" s="37">
+        <v>2.2905894897810898E-3</v>
+      </c>
+      <c r="C26" s="38">
+        <v>1.1220879540581999E-5</v>
+      </c>
+      <c r="D26" s="39">
+        <v>204.136358606903</v>
+      </c>
+      <c r="E26" s="40">
+        <v>4.4940286711434902E-58</v>
+      </c>
+      <c r="F26" s="38">
+        <v>2.2678538282274101E-3</v>
+      </c>
+      <c r="G26" s="38">
+        <v>2.31332515133478E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="69" t="s">
         <v>88</v>
       </c>
-      <c r="B26" s="46" t="n">
-        <v>0.00229058948978109</v>
-      </c>
-      <c r="C26" s="47" t="n">
-        <v>1.1220879540582E-005</v>
-      </c>
-      <c r="D26" s="48" t="n">
-        <v>204.136358606903</v>
-      </c>
-      <c r="E26" s="49" t="n">
-        <v>4.49402867114349E-058</v>
-      </c>
-      <c r="F26" s="47" t="n">
-        <v>0.00226785382822741</v>
-      </c>
-      <c r="G26" s="47" t="n">
-        <v>0.00231332515133478</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="55" t="s">
+      <c r="B29" s="69"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="55"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="56" t="s">
+      <c r="B30" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="B30" s="56" t="s">
+      <c r="C30" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="56" t="s">
+      <c r="D30" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="D30" s="56" t="s">
+      <c r="E30" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="E30" s="56" t="s">
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="14" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
+      <c r="B31" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="20" t="s">
+      <c r="C31" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="D31" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="E31" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="E31" s="57" t="s">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="48" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="58" t="s">
-        <v>95</v>
-      </c>
-      <c r="B32" s="58" t="s">
+      <c r="C32" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="59" t="s">
+      <c r="D32" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="E32" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="59" t="s">
-        <v>98</v>
-      </c>
-      <c r="E32" s="60" t="s">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="14" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="s">
+      <c r="B33" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="20" t="s">
+      <c r="C33" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="D33" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="E33" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="E33" s="61" t="s">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="48" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="B34" s="58" t="s">
+      <c r="C34" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34" s="52" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="59" t="s">
-        <v>105</v>
-      </c>
-      <c r="D34" s="59" t="s">
-        <v>106</v>
-      </c>
-      <c r="E34" s="62" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="B35" s="20" t="s">
+      <c r="C35" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="D35" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="E35" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="E35" s="57" t="s">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="48" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="58" t="s">
+      <c r="B36" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="B36" s="58" t="s">
+      <c r="C36" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="C36" s="59" t="s">
+      <c r="D36" s="49" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="59" t="s">
+      <c r="E36" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="E36" s="60" t="s">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="14" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="20" t="s">
+      <c r="B37" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B37" s="20" t="s">
+      <c r="C37" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="D37" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E37" s="51" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" s="48" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="E37" s="61" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="58" t="s">
-        <v>118</v>
-      </c>
-      <c r="B38" s="58" t="s">
+      <c r="C38" s="49" t="s">
         <v>121</v>
       </c>
-      <c r="C38" s="59" t="s">
+      <c r="D38" s="49" t="s">
         <v>122</v>
       </c>
-      <c r="D38" s="59" t="s">
+      <c r="E38" s="52" t="s">
         <v>123</v>
-      </c>
-      <c r="E38" s="62" t="s">
-        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -6928,1054 +7053,1046 @@
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A29:E29"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H50"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="65" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="G3" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="G3" s="29" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="29">
+        <v>1980</v>
+      </c>
+      <c r="B4" s="53">
+        <v>2852</v>
+      </c>
+      <c r="C4" s="28">
+        <v>2844.59</v>
+      </c>
+      <c r="D4" s="54">
+        <v>7.41</v>
+      </c>
+      <c r="E4" s="39">
+        <v>0.52359999999999995</v>
+      </c>
+      <c r="F4" s="53">
+        <v>716873</v>
+      </c>
+      <c r="G4" s="53">
+        <v>1318332</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="55">
+        <v>1981</v>
+      </c>
+      <c r="B5" s="56">
+        <v>2842</v>
+      </c>
+      <c r="C5" s="57">
+        <v>2836.07</v>
+      </c>
+      <c r="D5" s="58">
+        <v>5.93</v>
+      </c>
+      <c r="E5" s="44">
+        <v>0.41860000000000003</v>
+      </c>
+      <c r="F5" s="56">
+        <v>710789</v>
+      </c>
+      <c r="G5" s="56">
+        <v>1302921</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="29">
+        <v>1982</v>
+      </c>
+      <c r="B6" s="53">
+        <v>2762</v>
+      </c>
+      <c r="C6" s="28">
+        <v>2757.19</v>
+      </c>
+      <c r="D6" s="54">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="E6" s="39">
+        <v>0.33960000000000001</v>
+      </c>
+      <c r="F6" s="53">
+        <v>682070</v>
+      </c>
+      <c r="G6" s="53">
+        <v>1213281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="55">
+        <v>1983</v>
+      </c>
+      <c r="B7" s="56">
+        <v>2605</v>
+      </c>
+      <c r="C7" s="57">
+        <v>2608.09</v>
+      </c>
+      <c r="D7" s="58">
+        <v>-3.09</v>
+      </c>
+      <c r="E7" s="44">
+        <v>-0.218</v>
+      </c>
+      <c r="F7" s="56">
+        <v>665813</v>
+      </c>
+      <c r="G7" s="56">
+        <v>1116937</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="29">
+        <v>1984</v>
+      </c>
+      <c r="B8" s="53">
+        <v>2491</v>
+      </c>
+      <c r="C8" s="28">
+        <v>2517.79</v>
+      </c>
+      <c r="D8" s="54">
+        <v>-26.79</v>
+      </c>
+      <c r="E8" s="39">
+        <v>-1.8925000000000001</v>
+      </c>
+      <c r="F8" s="53">
+        <v>630833</v>
+      </c>
+      <c r="G8" s="53">
+        <v>1010279</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="55">
+        <v>1985</v>
+      </c>
+      <c r="B9" s="56">
+        <v>2975</v>
+      </c>
+      <c r="C9" s="57">
+        <v>2972.69</v>
+      </c>
+      <c r="D9" s="58">
+        <v>2.31</v>
+      </c>
+      <c r="E9" s="44">
+        <v>0.16320000000000001</v>
+      </c>
+      <c r="F9" s="56">
+        <v>656375</v>
+      </c>
+      <c r="G9" s="56">
+        <v>1257970</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="29">
+        <v>1986</v>
+      </c>
+      <c r="B10" s="53">
+        <v>2640</v>
+      </c>
+      <c r="C10" s="28">
+        <v>2645.37</v>
+      </c>
+      <c r="D10" s="54">
+        <v>-5.37</v>
+      </c>
+      <c r="E10" s="39">
+        <v>-0.37940000000000002</v>
+      </c>
+      <c r="F10" s="53">
+        <v>650875</v>
+      </c>
+      <c r="G10" s="53">
+        <v>1104501</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="55">
+        <v>1987</v>
+      </c>
+      <c r="B11" s="56">
+        <v>2469</v>
+      </c>
+      <c r="C11" s="57">
+        <v>2476.87</v>
+      </c>
+      <c r="D11" s="58">
+        <v>-7.87</v>
+      </c>
+      <c r="E11" s="44">
+        <v>-0.55579999999999996</v>
+      </c>
+      <c r="F11" s="56">
+        <v>658954</v>
+      </c>
+      <c r="G11" s="56">
+        <v>1046467</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="29">
+        <v>1988</v>
+      </c>
+      <c r="B12" s="53">
+        <v>2525</v>
+      </c>
+      <c r="C12" s="28">
+        <v>2523.61</v>
+      </c>
+      <c r="D12" s="54">
+        <v>1.39</v>
+      </c>
+      <c r="E12" s="39">
+        <v>9.8299999999999998E-2</v>
+      </c>
+      <c r="F12" s="53">
+        <v>671755</v>
+      </c>
+      <c r="G12" s="53">
+        <v>1091478</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="55">
+        <v>1989</v>
+      </c>
+      <c r="B13" s="56">
+        <v>2625</v>
+      </c>
+      <c r="C13" s="57">
+        <v>2628.48</v>
+      </c>
+      <c r="D13" s="58">
+        <v>-3.48</v>
+      </c>
+      <c r="E13" s="44">
+        <v>-0.2455</v>
+      </c>
+      <c r="F13" s="56">
+        <v>664137</v>
+      </c>
+      <c r="G13" s="56">
+        <v>1122617</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="29">
+        <v>1990</v>
+      </c>
+      <c r="B14" s="53">
+        <v>2769</v>
+      </c>
+      <c r="C14" s="28">
+        <v>2767.54</v>
+      </c>
+      <c r="D14" s="54">
+        <v>1.46</v>
+      </c>
+      <c r="E14" s="39">
+        <v>0.1028</v>
+      </c>
+      <c r="F14" s="53">
+        <v>680647</v>
+      </c>
+      <c r="G14" s="53">
+        <v>1215065</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="55">
+        <v>1991</v>
+      </c>
+      <c r="B15" s="56">
+        <v>2818</v>
+      </c>
+      <c r="C15" s="57">
+        <v>2815.6</v>
+      </c>
+      <c r="D15" s="58">
+        <v>2.4</v>
+      </c>
+      <c r="E15" s="44">
+        <v>0.16980000000000001</v>
+      </c>
+      <c r="F15" s="56">
+        <v>683640</v>
+      </c>
+      <c r="G15" s="56">
+        <v>1241796</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="29">
+        <v>1992</v>
+      </c>
+      <c r="B16" s="53">
+        <v>2992</v>
+      </c>
+      <c r="C16" s="28">
+        <v>2992.07</v>
+      </c>
+      <c r="D16" s="54">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="E16" s="39">
+        <v>-5.1999999999999998E-3</v>
+      </c>
+      <c r="F16" s="53">
+        <v>672753</v>
+      </c>
+      <c r="G16" s="53">
+        <v>1297914</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="55">
+        <v>1993</v>
+      </c>
+      <c r="B17" s="56">
+        <v>3035</v>
+      </c>
+      <c r="C17" s="57">
+        <v>3037.35</v>
+      </c>
+      <c r="D17" s="58">
+        <v>-2.35</v>
+      </c>
+      <c r="E17" s="44">
+        <v>-0.16589999999999999</v>
+      </c>
+      <c r="F17" s="56">
+        <v>693434</v>
+      </c>
+      <c r="G17" s="56">
+        <v>1357432</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="29">
+        <v>1994</v>
+      </c>
+      <c r="B18" s="53">
+        <v>3061</v>
+      </c>
+      <c r="C18" s="28">
+        <v>3063.78</v>
+      </c>
+      <c r="D18" s="54">
+        <v>-2.78</v>
+      </c>
+      <c r="E18" s="39">
+        <v>-0.1961</v>
+      </c>
+      <c r="F18" s="53">
+        <v>698624</v>
+      </c>
+      <c r="G18" s="53">
+        <v>1378945</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="55">
+        <v>1995</v>
+      </c>
+      <c r="B19" s="56">
+        <v>3162</v>
+      </c>
+      <c r="C19" s="57">
+        <v>3162.96</v>
+      </c>
+      <c r="D19" s="58">
+        <v>-0.96</v>
+      </c>
+      <c r="E19" s="44">
+        <v>-6.8000000000000005E-2</v>
+      </c>
+      <c r="F19" s="56">
+        <v>672787</v>
+      </c>
+      <c r="G19" s="56">
+        <v>1372584</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="29">
+        <v>1996</v>
+      </c>
+      <c r="B20" s="53">
+        <v>3251</v>
+      </c>
+      <c r="C20" s="28">
+        <v>3258.79</v>
+      </c>
+      <c r="D20" s="54">
+        <v>-7.79</v>
+      </c>
+      <c r="E20" s="39">
+        <v>-0.55030000000000001</v>
+      </c>
+      <c r="F20" s="53">
+        <v>685468</v>
+      </c>
+      <c r="G20" s="53">
+        <v>1438794</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="55">
+        <v>1997</v>
+      </c>
+      <c r="B21" s="56">
+        <v>3068</v>
+      </c>
+      <c r="C21" s="57">
+        <v>3072.27</v>
+      </c>
+      <c r="D21" s="58">
+        <v>-4.2699999999999996</v>
+      </c>
+      <c r="E21" s="44">
+        <v>-0.30170000000000002</v>
+      </c>
+      <c r="F21" s="56">
+        <v>690975</v>
+      </c>
+      <c r="G21" s="56">
+        <v>1367951</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="29">
+        <v>1998</v>
+      </c>
+      <c r="B22" s="53">
+        <v>2883</v>
+      </c>
+      <c r="C22" s="28">
+        <v>2890.75</v>
+      </c>
+      <c r="D22" s="54">
+        <v>-7.75</v>
+      </c>
+      <c r="E22" s="39">
+        <v>-0.54769999999999996</v>
+      </c>
+      <c r="F22" s="53">
+        <v>674404</v>
+      </c>
+      <c r="G22" s="53">
+        <v>1256854</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="55">
+        <v>1999</v>
+      </c>
+      <c r="B23" s="56">
+        <v>2941</v>
+      </c>
+      <c r="C23" s="57">
+        <v>2943.47</v>
+      </c>
+      <c r="D23" s="58">
+        <v>-2.4700000000000002</v>
+      </c>
+      <c r="E23" s="44">
+        <v>-0.17419999999999999</v>
+      </c>
+      <c r="F23" s="56">
+        <v>692389</v>
+      </c>
+      <c r="G23" s="56">
+        <v>1314437</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="29">
+        <v>2000</v>
+      </c>
+      <c r="B24" s="53">
+        <v>3064</v>
+      </c>
+      <c r="C24" s="28">
+        <v>3069.66</v>
+      </c>
+      <c r="D24" s="54">
+        <v>-5.66</v>
+      </c>
+      <c r="E24" s="39">
+        <v>-0.39950000000000002</v>
+      </c>
+      <c r="F24" s="53">
+        <v>698702</v>
+      </c>
+      <c r="G24" s="53">
+        <v>1381662</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="55">
+        <v>2001</v>
+      </c>
+      <c r="B25" s="56">
+        <v>3110</v>
+      </c>
+      <c r="C25" s="57">
+        <v>3110.85</v>
+      </c>
+      <c r="D25" s="58">
+        <v>-0.85</v>
+      </c>
+      <c r="E25" s="44">
+        <v>-0.06</v>
+      </c>
+      <c r="F25" s="56">
+        <v>673634</v>
+      </c>
+      <c r="G25" s="56">
+        <v>1351461</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="29">
+        <v>2002</v>
+      </c>
+      <c r="B26" s="53">
+        <v>3238</v>
+      </c>
+      <c r="C26" s="28">
+        <v>3235.04</v>
+      </c>
+      <c r="D26" s="54">
+        <v>2.96</v>
+      </c>
+      <c r="E26" s="39">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="F26" s="53">
+        <v>678544</v>
+      </c>
+      <c r="G26" s="53">
+        <v>1415117</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="55">
+        <v>2003</v>
+      </c>
+      <c r="B27" s="56">
+        <v>3360</v>
+      </c>
+      <c r="C27" s="57">
+        <v>3351.73</v>
+      </c>
+      <c r="D27" s="58">
+        <v>8.27</v>
+      </c>
+      <c r="E27" s="44">
+        <v>0.58389999999999997</v>
+      </c>
+      <c r="F27" s="56">
+        <v>671820</v>
+      </c>
+      <c r="G27" s="56">
+        <v>1453137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="29">
+        <v>2004</v>
+      </c>
+      <c r="B28" s="53">
+        <v>3434</v>
+      </c>
+      <c r="C28" s="28">
+        <v>3363.84</v>
+      </c>
+      <c r="D28" s="54">
+        <v>70.16</v>
+      </c>
+      <c r="E28" s="39">
+        <v>4.9562999999999997</v>
+      </c>
+      <c r="F28" s="53">
+        <v>676310</v>
+      </c>
+      <c r="G28" s="53">
+        <v>1467052</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="55">
+        <v>2005</v>
+      </c>
+      <c r="B29" s="56">
+        <v>3471</v>
+      </c>
+      <c r="C29" s="57">
+        <v>3458.39</v>
+      </c>
+      <c r="D29" s="58">
+        <v>12.61</v>
+      </c>
+      <c r="E29" s="44">
+        <v>0.89059999999999995</v>
+      </c>
+      <c r="F29" s="56">
+        <v>666781</v>
+      </c>
+      <c r="G29" s="56">
+        <v>1490015</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="29">
+        <v>2006</v>
+      </c>
+      <c r="B30" s="53">
+        <v>3236</v>
+      </c>
+      <c r="C30" s="28">
+        <v>3228</v>
+      </c>
+      <c r="D30" s="54">
+        <v>8</v>
+      </c>
+      <c r="E30" s="39">
+        <v>0.56489999999999996</v>
+      </c>
+      <c r="F30" s="53">
+        <v>676034</v>
+      </c>
+      <c r="G30" s="53">
+        <v>1407220</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="55">
+        <v>2007</v>
+      </c>
+      <c r="B31" s="56">
+        <v>3514</v>
+      </c>
+      <c r="C31" s="57">
+        <v>3511.13</v>
+      </c>
+      <c r="D31" s="58">
+        <v>2.87</v>
+      </c>
+      <c r="E31" s="44">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="F31" s="56">
+        <v>676111</v>
+      </c>
+      <c r="G31" s="56">
+        <v>1530971</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="29">
+        <v>2008</v>
+      </c>
+      <c r="B32" s="53">
+        <v>3584</v>
+      </c>
+      <c r="C32" s="28">
+        <v>3563.81</v>
+      </c>
+      <c r="D32" s="54">
+        <v>20.190000000000001</v>
+      </c>
+      <c r="E32" s="39">
+        <v>1.4265000000000001</v>
+      </c>
+      <c r="F32" s="53">
+        <v>656602</v>
+      </c>
+      <c r="G32" s="53">
+        <v>1516470</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="55">
+        <v>2009</v>
+      </c>
+      <c r="B33" s="56">
+        <v>3720</v>
+      </c>
+      <c r="C33" s="57">
+        <v>3720.86</v>
+      </c>
+      <c r="D33" s="58">
+        <v>-0.86</v>
+      </c>
+      <c r="E33" s="44">
+        <v>-6.0600000000000001E-2</v>
+      </c>
+      <c r="F33" s="56">
+        <v>674928</v>
+      </c>
+      <c r="G33" s="56">
+        <v>1620259</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="29">
+        <v>2010</v>
+      </c>
+      <c r="B34" s="53">
+        <v>3636</v>
+      </c>
+      <c r="C34" s="28">
+        <v>3635</v>
+      </c>
+      <c r="D34" s="54">
+        <v>1</v>
+      </c>
+      <c r="E34" s="39">
+        <v>7.0800000000000002E-2</v>
+      </c>
+      <c r="F34" s="53">
+        <v>677884</v>
+      </c>
+      <c r="G34" s="53">
+        <v>1588457</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="55">
+        <v>2011</v>
+      </c>
+      <c r="B35" s="56">
+        <v>3748</v>
+      </c>
+      <c r="C35" s="57">
+        <v>3757.48</v>
+      </c>
+      <c r="D35" s="58">
+        <v>-9.48</v>
+      </c>
+      <c r="E35" s="44">
+        <v>-0.66990000000000005</v>
+      </c>
+      <c r="F35" s="56">
+        <v>687940</v>
+      </c>
+      <c r="G35" s="56">
+        <v>1661260</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="29">
+        <v>2012</v>
+      </c>
+      <c r="B36" s="53">
+        <v>3797</v>
+      </c>
+      <c r="C36" s="28">
+        <v>3803.86</v>
+      </c>
+      <c r="D36" s="54">
+        <v>-6.86</v>
+      </c>
+      <c r="E36" s="39">
+        <v>-0.48470000000000002</v>
+      </c>
+      <c r="F36" s="53">
+        <v>684545</v>
+      </c>
+      <c r="G36" s="53">
+        <v>1674981</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="55">
+        <v>2013</v>
+      </c>
+      <c r="B37" s="56">
+        <v>3876</v>
+      </c>
+      <c r="C37" s="57">
+        <v>3865.98</v>
+      </c>
+      <c r="D37" s="58">
+        <v>10.02</v>
+      </c>
+      <c r="E37" s="44">
+        <v>0.70809999999999995</v>
+      </c>
+      <c r="F37" s="56">
+        <v>671679</v>
+      </c>
+      <c r="G37" s="56">
+        <v>1677368</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="29">
+        <v>2014</v>
+      </c>
+      <c r="B38" s="53">
+        <v>4194</v>
+      </c>
+      <c r="C38" s="28">
+        <v>4193.37</v>
+      </c>
+      <c r="D38" s="54">
+        <v>0.63</v>
+      </c>
+      <c r="E38" s="39">
+        <v>4.4299999999999999E-2</v>
+      </c>
+      <c r="F38" s="53">
+        <v>679239</v>
+      </c>
+      <c r="G38" s="53">
+        <v>1834831</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="55">
+        <v>2015</v>
+      </c>
+      <c r="B39" s="56">
+        <v>4022</v>
+      </c>
+      <c r="C39" s="57">
+        <v>4028.72</v>
+      </c>
+      <c r="D39" s="58">
+        <v>-6.72</v>
+      </c>
+      <c r="E39" s="44">
+        <v>-0.47460000000000002</v>
+      </c>
+      <c r="F39" s="56">
+        <v>681559</v>
+      </c>
+      <c r="G39" s="56">
+        <v>1767407</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="29">
+        <v>2016</v>
+      </c>
+      <c r="B40" s="53">
+        <v>3978</v>
+      </c>
+      <c r="C40" s="28">
+        <v>3994.01</v>
+      </c>
+      <c r="D40" s="54">
+        <v>-16.010000000000002</v>
+      </c>
+      <c r="E40" s="39">
+        <v>-1.1309</v>
+      </c>
+      <c r="F40" s="53">
+        <v>688770</v>
+      </c>
+      <c r="G40" s="53">
+        <v>1766115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="55">
+        <v>2017</v>
+      </c>
+      <c r="B41" s="56">
+        <v>3750</v>
+      </c>
+      <c r="C41" s="57">
+        <v>3756.66</v>
+      </c>
+      <c r="D41" s="58">
+        <v>-6.66</v>
+      </c>
+      <c r="E41" s="44">
+        <v>-0.47039999999999998</v>
+      </c>
+      <c r="F41" s="56">
+        <v>685548</v>
+      </c>
+      <c r="G41" s="56">
+        <v>1656302</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="29">
+        <v>2018</v>
+      </c>
+      <c r="B42" s="53">
+        <v>3770</v>
+      </c>
+      <c r="C42" s="28">
+        <v>3792.3</v>
+      </c>
+      <c r="D42" s="54">
+        <v>-22.3</v>
+      </c>
+      <c r="E42" s="39">
+        <v>-1.5755999999999999</v>
+      </c>
+      <c r="F42" s="53">
+        <v>700306</v>
+      </c>
+      <c r="G42" s="53">
+        <v>1700231</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="55">
+        <v>2019</v>
+      </c>
+      <c r="B43" s="56">
+        <v>4255</v>
+      </c>
+      <c r="C43" s="57">
+        <v>4266.99</v>
+      </c>
+      <c r="D43" s="58">
+        <v>-11.99</v>
+      </c>
+      <c r="E43" s="44">
+        <v>-0.84719999999999995</v>
+      </c>
+      <c r="F43" s="56">
+        <v>684416</v>
+      </c>
+      <c r="G43" s="56">
+        <v>1876922</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" s="74" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="37" t="n">
-        <v>1980</v>
-      </c>
-      <c r="B4" s="63" t="n">
-        <v>2852</v>
-      </c>
-      <c r="C4" s="36" t="n">
-        <v>2844.59</v>
-      </c>
-      <c r="D4" s="64" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="E4" s="48" t="n">
-        <v>0.5236</v>
-      </c>
-      <c r="F4" s="63" t="n">
-        <v>716873</v>
-      </c>
-      <c r="G4" s="63" t="n">
-        <v>1318332</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="65" t="n">
-        <v>1981</v>
-      </c>
-      <c r="B5" s="66" t="n">
-        <v>2842</v>
-      </c>
-      <c r="C5" s="67" t="n">
-        <v>2836.07</v>
-      </c>
-      <c r="D5" s="68" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="E5" s="53" t="n">
-        <v>0.4186</v>
-      </c>
-      <c r="F5" s="66" t="n">
-        <v>710789</v>
-      </c>
-      <c r="G5" s="66" t="n">
-        <v>1302921</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="37" t="n">
-        <v>1982</v>
-      </c>
-      <c r="B6" s="63" t="n">
-        <v>2762</v>
-      </c>
-      <c r="C6" s="36" t="n">
-        <v>2757.19</v>
-      </c>
-      <c r="D6" s="64" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="E6" s="48" t="n">
-        <v>0.3396</v>
-      </c>
-      <c r="F6" s="63" t="n">
-        <v>682070</v>
-      </c>
-      <c r="G6" s="63" t="n">
-        <v>1213281</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="65" t="n">
-        <v>1983</v>
-      </c>
-      <c r="B7" s="66" t="n">
-        <v>2605</v>
-      </c>
-      <c r="C7" s="67" t="n">
-        <v>2608.09</v>
-      </c>
-      <c r="D7" s="68" t="n">
-        <v>-3.09</v>
-      </c>
-      <c r="E7" s="53" t="n">
-        <v>-0.218</v>
-      </c>
-      <c r="F7" s="66" t="n">
-        <v>665813</v>
-      </c>
-      <c r="G7" s="66" t="n">
-        <v>1116937</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="n">
-        <v>1984</v>
-      </c>
-      <c r="B8" s="63" t="n">
-        <v>2491</v>
-      </c>
-      <c r="C8" s="36" t="n">
-        <v>2517.79</v>
-      </c>
-      <c r="D8" s="64" t="n">
-        <v>-26.79</v>
-      </c>
-      <c r="E8" s="48" t="n">
-        <v>-1.8925</v>
-      </c>
-      <c r="F8" s="63" t="n">
-        <v>630833</v>
-      </c>
-      <c r="G8" s="63" t="n">
-        <v>1010279</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="65" t="n">
-        <v>1985</v>
-      </c>
-      <c r="B9" s="66" t="n">
-        <v>2975</v>
-      </c>
-      <c r="C9" s="67" t="n">
-        <v>2972.69</v>
-      </c>
-      <c r="D9" s="68" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="E9" s="53" t="n">
-        <v>0.1632</v>
-      </c>
-      <c r="F9" s="66" t="n">
-        <v>656375</v>
-      </c>
-      <c r="G9" s="66" t="n">
-        <v>1257970</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37" t="n">
-        <v>1986</v>
-      </c>
-      <c r="B10" s="63" t="n">
-        <v>2640</v>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>2645.37</v>
-      </c>
-      <c r="D10" s="64" t="n">
-        <v>-5.37</v>
-      </c>
-      <c r="E10" s="48" t="n">
-        <v>-0.3794</v>
-      </c>
-      <c r="F10" s="63" t="n">
-        <v>650875</v>
-      </c>
-      <c r="G10" s="63" t="n">
-        <v>1104501</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="65" t="n">
-        <v>1987</v>
-      </c>
-      <c r="B11" s="66" t="n">
-        <v>2469</v>
-      </c>
-      <c r="C11" s="67" t="n">
-        <v>2476.87</v>
-      </c>
-      <c r="D11" s="68" t="n">
-        <v>-7.87</v>
-      </c>
-      <c r="E11" s="53" t="n">
-        <v>-0.5558</v>
-      </c>
-      <c r="F11" s="66" t="n">
-        <v>658954</v>
-      </c>
-      <c r="G11" s="66" t="n">
-        <v>1046467</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="n">
-        <v>1988</v>
-      </c>
-      <c r="B12" s="63" t="n">
-        <v>2525</v>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>2523.61</v>
-      </c>
-      <c r="D12" s="64" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E12" s="48" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="F12" s="63" t="n">
-        <v>671755</v>
-      </c>
-      <c r="G12" s="63" t="n">
-        <v>1091478</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="65" t="n">
-        <v>1989</v>
-      </c>
-      <c r="B13" s="66" t="n">
-        <v>2625</v>
-      </c>
-      <c r="C13" s="67" t="n">
-        <v>2628.48</v>
-      </c>
-      <c r="D13" s="68" t="n">
-        <v>-3.48</v>
-      </c>
-      <c r="E13" s="53" t="n">
-        <v>-0.2455</v>
-      </c>
-      <c r="F13" s="66" t="n">
-        <v>664137</v>
-      </c>
-      <c r="G13" s="66" t="n">
-        <v>1122617</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="n">
-        <v>1990</v>
-      </c>
-      <c r="B14" s="63" t="n">
-        <v>2769</v>
-      </c>
-      <c r="C14" s="36" t="n">
-        <v>2767.54</v>
-      </c>
-      <c r="D14" s="64" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E14" s="48" t="n">
-        <v>0.1028</v>
-      </c>
-      <c r="F14" s="63" t="n">
-        <v>680647</v>
-      </c>
-      <c r="G14" s="63" t="n">
-        <v>1215065</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="65" t="n">
-        <v>1991</v>
-      </c>
-      <c r="B15" s="66" t="n">
-        <v>2818</v>
-      </c>
-      <c r="C15" s="67" t="n">
-        <v>2815.6</v>
-      </c>
-      <c r="D15" s="68" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E15" s="53" t="n">
-        <v>0.1698</v>
-      </c>
-      <c r="F15" s="66" t="n">
-        <v>683640</v>
-      </c>
-      <c r="G15" s="66" t="n">
-        <v>1241796</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="37" t="n">
-        <v>1992</v>
-      </c>
-      <c r="B16" s="63" t="n">
-        <v>2992</v>
-      </c>
-      <c r="C16" s="36" t="n">
-        <v>2992.07</v>
-      </c>
-      <c r="D16" s="64" t="n">
-        <v>-0.07</v>
-      </c>
-      <c r="E16" s="48" t="n">
-        <v>-0.0052</v>
-      </c>
-      <c r="F16" s="63" t="n">
-        <v>672753</v>
-      </c>
-      <c r="G16" s="63" t="n">
-        <v>1297914</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="65" t="n">
-        <v>1993</v>
-      </c>
-      <c r="B17" s="66" t="n">
-        <v>3035</v>
-      </c>
-      <c r="C17" s="67" t="n">
-        <v>3037.35</v>
-      </c>
-      <c r="D17" s="68" t="n">
-        <v>-2.35</v>
-      </c>
-      <c r="E17" s="53" t="n">
-        <v>-0.1659</v>
-      </c>
-      <c r="F17" s="66" t="n">
-        <v>693434</v>
-      </c>
-      <c r="G17" s="66" t="n">
-        <v>1357432</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="37" t="n">
-        <v>1994</v>
-      </c>
-      <c r="B18" s="63" t="n">
-        <v>3061</v>
-      </c>
-      <c r="C18" s="36" t="n">
-        <v>3063.78</v>
-      </c>
-      <c r="D18" s="64" t="n">
-        <v>-2.78</v>
-      </c>
-      <c r="E18" s="48" t="n">
-        <v>-0.1961</v>
-      </c>
-      <c r="F18" s="63" t="n">
-        <v>698624</v>
-      </c>
-      <c r="G18" s="63" t="n">
-        <v>1378945</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="65" t="n">
-        <v>1995</v>
-      </c>
-      <c r="B19" s="66" t="n">
-        <v>3162</v>
-      </c>
-      <c r="C19" s="67" t="n">
-        <v>3162.96</v>
-      </c>
-      <c r="D19" s="68" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="E19" s="53" t="n">
-        <v>-0.068</v>
-      </c>
-      <c r="F19" s="66" t="n">
-        <v>672787</v>
-      </c>
-      <c r="G19" s="66" t="n">
-        <v>1372584</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="37" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B20" s="63" t="n">
-        <v>3251</v>
-      </c>
-      <c r="C20" s="36" t="n">
-        <v>3258.79</v>
-      </c>
-      <c r="D20" s="64" t="n">
-        <v>-7.79</v>
-      </c>
-      <c r="E20" s="48" t="n">
-        <v>-0.5503</v>
-      </c>
-      <c r="F20" s="63" t="n">
-        <v>685468</v>
-      </c>
-      <c r="G20" s="63" t="n">
-        <v>1438794</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="65" t="n">
-        <v>1997</v>
-      </c>
-      <c r="B21" s="66" t="n">
-        <v>3068</v>
-      </c>
-      <c r="C21" s="67" t="n">
-        <v>3072.27</v>
-      </c>
-      <c r="D21" s="68" t="n">
-        <v>-4.27</v>
-      </c>
-      <c r="E21" s="53" t="n">
-        <v>-0.3017</v>
-      </c>
-      <c r="F21" s="66" t="n">
-        <v>690975</v>
-      </c>
-      <c r="G21" s="66" t="n">
-        <v>1367951</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="37" t="n">
-        <v>1998</v>
-      </c>
-      <c r="B22" s="63" t="n">
-        <v>2883</v>
-      </c>
-      <c r="C22" s="36" t="n">
-        <v>2890.75</v>
-      </c>
-      <c r="D22" s="64" t="n">
-        <v>-7.75</v>
-      </c>
-      <c r="E22" s="48" t="n">
-        <v>-0.5477</v>
-      </c>
-      <c r="F22" s="63" t="n">
-        <v>674404</v>
-      </c>
-      <c r="G22" s="63" t="n">
-        <v>1256854</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="65" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B23" s="66" t="n">
-        <v>2941</v>
-      </c>
-      <c r="C23" s="67" t="n">
-        <v>2943.47</v>
-      </c>
-      <c r="D23" s="68" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="E23" s="53" t="n">
-        <v>-0.1742</v>
-      </c>
-      <c r="F23" s="66" t="n">
-        <v>692389</v>
-      </c>
-      <c r="G23" s="66" t="n">
-        <v>1314437</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="37" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B24" s="63" t="n">
-        <v>3064</v>
-      </c>
-      <c r="C24" s="36" t="n">
-        <v>3069.66</v>
-      </c>
-      <c r="D24" s="64" t="n">
-        <v>-5.66</v>
-      </c>
-      <c r="E24" s="48" t="n">
-        <v>-0.3995</v>
-      </c>
-      <c r="F24" s="63" t="n">
-        <v>698702</v>
-      </c>
-      <c r="G24" s="63" t="n">
-        <v>1381662</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="65" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B25" s="66" t="n">
-        <v>3110</v>
-      </c>
-      <c r="C25" s="67" t="n">
-        <v>3110.85</v>
-      </c>
-      <c r="D25" s="68" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="E25" s="53" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="F25" s="66" t="n">
-        <v>673634</v>
-      </c>
-      <c r="G25" s="66" t="n">
-        <v>1351461</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="37" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B26" s="63" t="n">
-        <v>3238</v>
-      </c>
-      <c r="C26" s="36" t="n">
-        <v>3235.04</v>
-      </c>
-      <c r="D26" s="64" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="E26" s="48" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="F26" s="63" t="n">
-        <v>678544</v>
-      </c>
-      <c r="G26" s="63" t="n">
-        <v>1415117</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="65" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B27" s="66" t="n">
-        <v>3360</v>
-      </c>
-      <c r="C27" s="67" t="n">
-        <v>3351.73</v>
-      </c>
-      <c r="D27" s="68" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="E27" s="53" t="n">
-        <v>0.5839</v>
-      </c>
-      <c r="F27" s="66" t="n">
-        <v>671820</v>
-      </c>
-      <c r="G27" s="66" t="n">
-        <v>1453137</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="37" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B28" s="63" t="n">
-        <v>3434</v>
-      </c>
-      <c r="C28" s="36" t="n">
-        <v>3363.84</v>
-      </c>
-      <c r="D28" s="64" t="n">
-        <v>70.16</v>
-      </c>
-      <c r="E28" s="48" t="n">
-        <v>4.9563</v>
-      </c>
-      <c r="F28" s="63" t="n">
-        <v>676310</v>
-      </c>
-      <c r="G28" s="63" t="n">
-        <v>1467052</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="65" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B29" s="66" t="n">
-        <v>3471</v>
-      </c>
-      <c r="C29" s="67" t="n">
-        <v>3458.39</v>
-      </c>
-      <c r="D29" s="68" t="n">
-        <v>12.61</v>
-      </c>
-      <c r="E29" s="53" t="n">
-        <v>0.8906</v>
-      </c>
-      <c r="F29" s="66" t="n">
-        <v>666781</v>
-      </c>
-      <c r="G29" s="66" t="n">
-        <v>1490015</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="37" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B30" s="63" t="n">
-        <v>3236</v>
-      </c>
-      <c r="C30" s="36" t="n">
-        <v>3228</v>
-      </c>
-      <c r="D30" s="64" t="n">
-        <v>8</v>
-      </c>
-      <c r="E30" s="48" t="n">
-        <v>0.5649</v>
-      </c>
-      <c r="F30" s="63" t="n">
-        <v>676034</v>
-      </c>
-      <c r="G30" s="63" t="n">
-        <v>1407220</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="65" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B31" s="66" t="n">
-        <v>3514</v>
-      </c>
-      <c r="C31" s="67" t="n">
-        <v>3511.13</v>
-      </c>
-      <c r="D31" s="68" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E31" s="53" t="n">
-        <v>0.203</v>
-      </c>
-      <c r="F31" s="66" t="n">
-        <v>676111</v>
-      </c>
-      <c r="G31" s="66" t="n">
-        <v>1530971</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="37" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B32" s="63" t="n">
-        <v>3584</v>
-      </c>
-      <c r="C32" s="36" t="n">
-        <v>3563.81</v>
-      </c>
-      <c r="D32" s="64" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="E32" s="48" t="n">
-        <v>1.4265</v>
-      </c>
-      <c r="F32" s="63" t="n">
-        <v>656602</v>
-      </c>
-      <c r="G32" s="63" t="n">
-        <v>1516470</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="65" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B33" s="66" t="n">
-        <v>3720</v>
-      </c>
-      <c r="C33" s="67" t="n">
-        <v>3720.86</v>
-      </c>
-      <c r="D33" s="68" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="E33" s="53" t="n">
-        <v>-0.0606</v>
-      </c>
-      <c r="F33" s="66" t="n">
-        <v>674928</v>
-      </c>
-      <c r="G33" s="66" t="n">
-        <v>1620259</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="37" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B34" s="63" t="n">
-        <v>3636</v>
-      </c>
-      <c r="C34" s="36" t="n">
-        <v>3635</v>
-      </c>
-      <c r="D34" s="64" t="n">
+      <c r="B46" s="74"/>
+      <c r="C46" s="74"/>
+      <c r="D46" s="74"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="59"/>
+      <c r="B47" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B48" s="60">
         <v>1</v>
       </c>
-      <c r="E34" s="48" t="n">
-        <v>0.0708</v>
-      </c>
-      <c r="F34" s="63" t="n">
-        <v>677884</v>
-      </c>
-      <c r="G34" s="63" t="n">
-        <v>1588457</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="65" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B35" s="66" t="n">
-        <v>3748</v>
-      </c>
-      <c r="C35" s="67" t="n">
-        <v>3757.48</v>
-      </c>
-      <c r="D35" s="68" t="n">
-        <v>-9.48</v>
-      </c>
-      <c r="E35" s="53" t="n">
-        <v>-0.6699</v>
-      </c>
-      <c r="F35" s="66" t="n">
-        <v>687940</v>
-      </c>
-      <c r="G35" s="66" t="n">
-        <v>1661260</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="37" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B36" s="63" t="n">
-        <v>3797</v>
-      </c>
-      <c r="C36" s="36" t="n">
-        <v>3803.86</v>
-      </c>
-      <c r="D36" s="64" t="n">
-        <v>-6.86</v>
-      </c>
-      <c r="E36" s="48" t="n">
-        <v>-0.4847</v>
-      </c>
-      <c r="F36" s="63" t="n">
-        <v>684545</v>
-      </c>
-      <c r="G36" s="63" t="n">
-        <v>1674981</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="65" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B37" s="66" t="n">
-        <v>3876</v>
-      </c>
-      <c r="C37" s="67" t="n">
-        <v>3865.98</v>
-      </c>
-      <c r="D37" s="68" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="E37" s="53" t="n">
-        <v>0.7081</v>
-      </c>
-      <c r="F37" s="66" t="n">
-        <v>671679</v>
-      </c>
-      <c r="G37" s="66" t="n">
-        <v>1677368</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="37" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B38" s="63" t="n">
-        <v>4194</v>
-      </c>
-      <c r="C38" s="36" t="n">
-        <v>4193.37</v>
-      </c>
-      <c r="D38" s="64" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E38" s="48" t="n">
-        <v>0.0443</v>
-      </c>
-      <c r="F38" s="63" t="n">
-        <v>679239</v>
-      </c>
-      <c r="G38" s="63" t="n">
-        <v>1834831</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="65" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B39" s="66" t="n">
-        <v>4022</v>
-      </c>
-      <c r="C39" s="67" t="n">
-        <v>4028.72</v>
-      </c>
-      <c r="D39" s="68" t="n">
-        <v>-6.72</v>
-      </c>
-      <c r="E39" s="53" t="n">
-        <v>-0.4746</v>
-      </c>
-      <c r="F39" s="66" t="n">
-        <v>681559</v>
-      </c>
-      <c r="G39" s="66" t="n">
-        <v>1767407</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="37" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B40" s="63" t="n">
-        <v>3978</v>
-      </c>
-      <c r="C40" s="36" t="n">
-        <v>3994.01</v>
-      </c>
-      <c r="D40" s="64" t="n">
-        <v>-16.01</v>
-      </c>
-      <c r="E40" s="48" t="n">
-        <v>-1.1309</v>
-      </c>
-      <c r="F40" s="63" t="n">
-        <v>688770</v>
-      </c>
-      <c r="G40" s="63" t="n">
-        <v>1766115</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="65" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B41" s="66" t="n">
-        <v>3750</v>
-      </c>
-      <c r="C41" s="67" t="n">
-        <v>3756.66</v>
-      </c>
-      <c r="D41" s="68" t="n">
-        <v>-6.66</v>
-      </c>
-      <c r="E41" s="53" t="n">
-        <v>-0.4704</v>
-      </c>
-      <c r="F41" s="66" t="n">
-        <v>685548</v>
-      </c>
-      <c r="G41" s="66" t="n">
-        <v>1656302</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="37" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B42" s="63" t="n">
-        <v>3770</v>
-      </c>
-      <c r="C42" s="36" t="n">
-        <v>3792.3</v>
-      </c>
-      <c r="D42" s="64" t="n">
-        <v>-22.3</v>
-      </c>
-      <c r="E42" s="48" t="n">
-        <v>-1.5756</v>
-      </c>
-      <c r="F42" s="63" t="n">
-        <v>700306</v>
-      </c>
-      <c r="G42" s="63" t="n">
-        <v>1700231</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="65" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B43" s="66" t="n">
-        <v>4255</v>
-      </c>
-      <c r="C43" s="67" t="n">
-        <v>4266.99</v>
-      </c>
-      <c r="D43" s="68" t="n">
-        <v>-11.99</v>
-      </c>
-      <c r="E43" s="53" t="n">
-        <v>-0.8472</v>
-      </c>
-      <c r="F43" s="66" t="n">
-        <v>684416</v>
-      </c>
-      <c r="G43" s="66" t="n">
-        <v>1876922</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="12" t="s">
+      <c r="C48" s="44">
+        <v>0.35880000000000001</v>
+      </c>
+      <c r="D48" s="44">
+        <v>0.2316</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="69"/>
-      <c r="B47" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C47" s="3" t="s">
+      <c r="B49" s="44">
+        <v>0.35880000000000001</v>
+      </c>
+      <c r="C49" s="60">
+        <v>1</v>
+      </c>
+      <c r="D49" s="60">
+        <v>0.99070000000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B48" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="53" t="n">
-        <v>0.3588</v>
-      </c>
-      <c r="D48" s="53" t="n">
+      <c r="B50" s="44">
         <v>0.2316</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B49" s="53" t="n">
-        <v>0.3588</v>
-      </c>
-      <c r="C49" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="70" t="n">
-        <v>0.9907</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B50" s="53" t="n">
-        <v>0.2316</v>
-      </c>
-      <c r="C50" s="70" t="n">
-        <v>0.9907</v>
-      </c>
-      <c r="D50" s="70" t="n">
+      <c r="C50" s="60">
+        <v>0.99070000000000003</v>
+      </c>
+      <c r="D50" s="60">
         <v>1</v>
       </c>
     </row>
@@ -7984,168 +8101,160 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A46:D46"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="1" style="0" width="9"/>
+    <col min="1" max="16" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="71" t="s">
+    <row r="1" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="80" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="80"/>
+      <c r="P1" s="80"/>
+    </row>
+    <row r="2" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="81" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
+    </row>
+    <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="82" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-    </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="72" t="s">
+      <c r="B4" s="82"/>
+      <c r="C4" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72"/>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="73" t="s">
+      <c r="D4" s="82"/>
+      <c r="E4" s="83" t="s">
         <v>136</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73" t="s">
+      <c r="F4" s="83"/>
+      <c r="G4" s="84" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84" t="s">
+        <v>74</v>
+      </c>
+      <c r="J4" s="84"/>
+      <c r="K4" s="85" t="s">
         <v>137</v>
       </c>
-      <c r="D4" s="73"/>
-      <c r="E4" s="74" t="s">
+      <c r="L4" s="85"/>
+      <c r="M4" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="F4" s="74"/>
-      <c r="G4" s="75" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75" t="s">
-        <v>75</v>
-      </c>
-      <c r="J4" s="75"/>
-      <c r="K4" s="76" t="s">
+      <c r="N4" s="85"/>
+      <c r="O4" s="85" t="s">
         <v>139</v>
       </c>
-      <c r="L4" s="76"/>
-      <c r="M4" s="76" t="s">
+      <c r="P4" s="85"/>
+    </row>
+    <row r="5" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="77" t="s">
         <v>140</v>
-      </c>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76" t="s">
-        <v>141</v>
-      </c>
-      <c r="P4" s="76"/>
-    </row>
-    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="77" t="s">
-        <v>142</v>
       </c>
       <c r="B5" s="77"/>
       <c r="C5" s="77" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D5" s="77"/>
       <c r="E5" s="78" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F5" s="78"/>
       <c r="G5" s="79" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H5" s="79"/>
       <c r="I5" s="79" t="s">
+        <v>144</v>
+      </c>
+      <c r="J5" s="79"/>
+      <c r="K5" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="N5" s="75"/>
+      <c r="O5" s="75" t="s">
         <v>146</v>
       </c>
-      <c r="J5" s="79"/>
-      <c r="K5" s="80" t="s">
+      <c r="P5" s="75"/>
+    </row>
+    <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="76" t="s">
         <v>147</v>
       </c>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80" t="s">
-        <v>147</v>
-      </c>
-      <c r="N5" s="80"/>
-      <c r="O5" s="80" t="s">
+      <c r="B6" s="76"/>
+      <c r="C6" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="P5" s="80"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="81" t="s">
+      <c r="D6" s="76"/>
+      <c r="E6" s="76" t="s">
         <v>149</v>
       </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="81" t="s">
+      <c r="F6" s="76"/>
+      <c r="G6" s="76" t="s">
         <v>150</v>
       </c>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81" t="s">
+      <c r="H6" s="76"/>
+      <c r="I6" s="76" t="s">
         <v>151</v>
       </c>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81" t="s">
+      <c r="J6" s="76"/>
+      <c r="K6" s="76" t="s">
+        <v>102</v>
+      </c>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76" t="s">
+        <v>102</v>
+      </c>
+      <c r="N6" s="76"/>
+      <c r="O6" s="76" t="s">
         <v>152</v>
       </c>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81" t="s">
-        <v>153</v>
-      </c>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81" t="s">
-        <v>103</v>
-      </c>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81" t="s">
-        <v>103</v>
-      </c>
-      <c r="N6" s="81"/>
-      <c r="O6" s="81" t="s">
-        <v>154</v>
-      </c>
-      <c r="P6" s="81"/>
+      <c r="P6" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -8159,11 +8268,6 @@
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="O4:P4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="M5:N5"/>
     <mergeCell ref="O5:P5"/>
@@ -8175,91 +8279,83 @@
     <mergeCell ref="K6:L6"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="O6:P6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="90"/>
+    <col min="1" max="1" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="82" t="s">
+    <row r="1" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="61" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="83" t="s">
+    <row r="3" spans="1:1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="62" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="63" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="62" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="84" t="s">
+    <row r="6" spans="1:1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="63" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="83" t="s">
+    <row r="7" spans="1:1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="62" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="84" t="s">
+    <row r="8" spans="1:1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="63" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="83" t="s">
+    <row r="9" spans="1:1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="62" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="84" t="s">
+    <row r="10" spans="1:1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="63" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="83" t="s">
+    <row r="11" spans="1:1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="62" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="84" t="s">
+    <row r="12" spans="1:1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="64" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="83" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="84" t="s">
-        <v>165</v>
-      </c>
-    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>